--- a/data/0.rule.xlsx
+++ b/data/0.rule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="10620"/>
+    <workbookView windowWidth="28800" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="基础维护对照表" sheetId="1" r:id="rId1"/>
@@ -1869,11 +1869,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
       <t>胎体帘线接头开</t>
     </r>
     <r>
@@ -3151,12 +3146,17 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3169,11 +3169,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3704,6 +3699,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -3712,32 +3720,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -3761,6 +3743,19 @@
         <color auto="1"/>
       </right>
       <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -4136,6 +4131,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4154,42 +4155,96 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4199,142 +4254,88 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4349,13 +4350,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4691,13 +4686,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -4998,23 +4986,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:X168"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="2.66666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.2222222222222" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.2222222222222" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.3703703703704" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.3240740740741" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.225" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.225" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.3666666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.8916666666667" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.325" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.66666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.11111111111111" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.4444444444444" style="5" customWidth="1"/>
-    <col min="10" max="10" width="6.55555555555556" style="5" customWidth="1"/>
-    <col min="11" max="11" width="12.4444444444444" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.88888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.10833333333333" style="5" customWidth="1"/>
+    <col min="9" max="9" width="12.4416666666667" style="5" customWidth="1"/>
+    <col min="10" max="10" width="6.55833333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="12.4416666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.89166666666667" style="1" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" style="6" customWidth="1"/>
-    <col min="14" max="14" width="6.88888888888889" style="5" customWidth="1"/>
-    <col min="15" max="15" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.89166666666667" style="5" customWidth="1"/>
+    <col min="15" max="15" width="14.1083333333333" style="1" customWidth="1"/>
     <col min="16" max="16" width="16.6666666666667" style="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="5"/>
     <col min="18" max="20" width="9" style="1"/>
@@ -5025,165 +5013,165 @@
     <col min="25" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.15" spans="2:22">
+    <row r="1" ht="18.75" spans="2:24">
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="36"/>
-      <c r="V1" s="51"/>
-    </row>
-    <row r="2" ht="18.15" spans="2:24">
-      <c r="B2" s="10" t="s">
+      <c r="U1" s="10"/>
+      <c r="V1" s="11"/>
+    </row>
+    <row r="2" ht="18" spans="2:24">
+      <c r="B2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="X2" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:24">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="25" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="26">
         <v>2025</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="43" t="s">
+      <c r="L3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="43">
+      <c r="M3" s="28">
         <v>48</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44" t="str">
+      <c r="O3" s="29"/>
+      <c r="P3" s="29" t="str">
         <f t="shared" ref="P3:P66" si="0">N3&amp;O3</f>
         <v>RD</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="R3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="S3" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" s="53" t="s">
+      <c r="S3" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="53" t="s">
+      <c r="V3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W3" s="54" t="s">
+      <c r="W3" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="X3" s="54" t="s">
+      <c r="X3" s="32" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="16.35" spans="2:24">
-      <c r="B4" s="21" t="s">
+    <row r="4" ht="17.25" spans="2:24">
+      <c r="B4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="36" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="7" t="s">
@@ -5192,22 +5180,22 @@
       <c r="G4" s="7">
         <v>4</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="25">
         <v>1</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="46">
+      <c r="J4" s="38">
         <v>2026</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="40">
         <v>48</v>
       </c>
       <c r="N4" s="7" t="s">
@@ -5224,36 +5212,36 @@
       <c r="R4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="S4" s="55" t="s">
+      <c r="S4" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="T4" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="53" t="s">
+      <c r="T4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W4" s="56" t="s">
+      <c r="W4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="X4" s="56" t="s">
+      <c r="X4" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="16.35" spans="2:24">
-      <c r="B5" s="21" t="s">
+    <row r="5" ht="17.25" spans="2:24">
+      <c r="B5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="36" t="s">
         <v>47</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -5262,22 +5250,22 @@
       <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="43">
         <v>2</v>
       </c>
-      <c r="I5" s="45" t="s">
+      <c r="I5" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="38">
         <v>2027</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="40">
         <v>48</v>
       </c>
       <c r="N5" s="7" t="s">
@@ -5296,34 +5284,34 @@
       <c r="R5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="46"/>
-      <c r="T5" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" s="53" t="s">
+      <c r="S5" s="38"/>
+      <c r="T5" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="V5" s="53" t="s">
+      <c r="V5" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W5" s="56" t="s">
+      <c r="W5" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="X5" s="14" t="s">
+      <c r="X5" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:24">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="36" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -5332,19 +5320,19 @@
       <c r="G6" s="7">
         <v>5</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="43">
         <v>3</v>
       </c>
-      <c r="I6" s="48" t="s">
+      <c r="I6" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="40">
         <v>48</v>
       </c>
       <c r="N6" s="7" t="s">
@@ -5363,33 +5351,33 @@
       <c r="R6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="53" t="s">
+      <c r="T6" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U6" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="V6" s="53" t="s">
+      <c r="V6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W6" s="56" t="s">
+      <c r="W6" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="54" t="s">
+      <c r="X6" s="32" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:23">
-      <c r="B7" s="21" t="s">
+    <row r="7" spans="2:24">
+      <c r="B7" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="36" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -5398,19 +5386,19 @@
       <c r="G7" s="7">
         <v>7</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="43">
         <v>4</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="47" t="s">
+      <c r="K7" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="L7" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="40">
         <v>48</v>
       </c>
       <c r="N7" s="7" t="s">
@@ -5426,30 +5414,30 @@
       <c r="Q7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="T7" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U7" s="53" t="s">
+      <c r="T7" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U7" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="V7" s="53" t="s">
+      <c r="V7" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W7" s="56" t="s">
+      <c r="W7" s="42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="2:23">
-      <c r="B8" s="21" t="s">
+    <row r="8" spans="2:24">
+      <c r="B8" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="36" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -5458,19 +5446,19 @@
       <c r="G8" s="7">
         <v>6</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="43">
         <v>5</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="40">
         <v>48</v>
       </c>
       <c r="N8" s="7" t="s">
@@ -5486,51 +5474,51 @@
       <c r="Q8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U8" s="53" t="s">
+      <c r="T8" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U8" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="V8" s="53" t="s">
+      <c r="V8" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W8" s="56" t="s">
+      <c r="W8" s="42" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="2:23">
-      <c r="B9" s="21" t="s">
+    <row r="9" spans="2:24">
+      <c r="B9" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="36" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="43">
         <v>6</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="L9" s="43" t="s">
+      <c r="L9" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="40">
         <v>48</v>
       </c>
       <c r="N9" s="7" t="s">
@@ -5544,30 +5532,30 @@
       <c r="Q9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="T9" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U9" s="53" t="s">
+      <c r="T9" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U9" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="V9" s="53" t="s">
+      <c r="V9" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W9" s="56" t="s">
+      <c r="W9" s="42" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="2:23">
-      <c r="B10" s="21" t="s">
+    <row r="10" spans="2:24">
+      <c r="B10" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="36" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -5576,19 +5564,19 @@
       <c r="G10" s="7">
         <v>3</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="43">
         <v>7</v>
       </c>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="L10" s="43" t="s">
+      <c r="L10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="40">
         <v>48</v>
       </c>
       <c r="N10" s="7" t="s">
@@ -5602,47 +5590,47 @@
       <c r="Q10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="T10" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U10" s="53" t="s">
+      <c r="T10" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="V10" s="53" t="s">
+      <c r="V10" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W10" s="56" t="s">
+      <c r="W10" s="42" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="2:23">
-      <c r="B11" s="21" t="s">
+    <row r="11" spans="2:24">
+      <c r="B11" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="25">
+      <c r="H11" s="43">
         <v>8</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="43" t="s">
+      <c r="L11" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="40">
         <v>48</v>
       </c>
       <c r="N11" s="7" t="s">
@@ -5656,52 +5644,52 @@
       <c r="Q11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="T11" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U11" s="53" t="s">
+      <c r="T11" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U11" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="V11" s="53" t="s">
+      <c r="V11" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W11" s="56" t="s">
+      <c r="W11" s="42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="2:23">
-      <c r="B12" s="21" t="s">
+    <row r="12" spans="2:24">
+      <c r="B12" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="25">
+      <c r="G12" s="45"/>
+      <c r="H12" s="43">
         <v>9</v>
       </c>
-      <c r="I12" s="48" t="s">
+      <c r="I12" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="L12" s="43" t="s">
+      <c r="L12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="40">
         <v>48</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="O12" s="49"/>
+      <c r="O12" s="46"/>
       <c r="P12" s="8" t="str">
         <f t="shared" si="0"/>
         <v>DC</v>
@@ -5709,45 +5697,45 @@
       <c r="Q12" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="T12" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U12" s="53" t="s">
+      <c r="T12" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U12" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="V12" s="53" t="s">
+      <c r="V12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="56" t="s">
+      <c r="W12" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:23">
-      <c r="B13" s="21" t="s">
+    <row r="13" spans="2:24">
+      <c r="B13" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="43">
         <v>10</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="43" t="s">
+      <c r="L13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="40">
         <v>48</v>
       </c>
       <c r="N13" s="7" t="s">
@@ -5761,45 +5749,45 @@
       <c r="Q13" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="T13" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U13" s="53" t="s">
+      <c r="T13" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U13" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="V13" s="53" t="s">
+      <c r="V13" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W13" s="56" t="s">
+      <c r="W13" s="42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:23">
-      <c r="B14" s="21" t="s">
+    <row r="14" spans="2:24">
+      <c r="B14" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="43">
         <v>11</v>
       </c>
-      <c r="I14" s="48" t="s">
+      <c r="I14" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="K14" s="47" t="s">
+      <c r="K14" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="L14" s="43" t="s">
+      <c r="L14" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="40">
         <v>48</v>
       </c>
       <c r="N14" s="7" t="s">
@@ -5813,45 +5801,45 @@
       <c r="Q14" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="T14" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U14" s="53" t="s">
+      <c r="T14" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U14" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="V14" s="53" t="s">
+      <c r="V14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W14" s="56" t="s">
+      <c r="W14" s="42" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="16.35" spans="2:23">
-      <c r="B15" s="21" t="s">
+    <row r="15" ht="17.25" spans="2:24">
+      <c r="B15" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="43">
         <v>12</v>
       </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="L15" s="43" t="s">
+      <c r="L15" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="40">
         <v>48</v>
       </c>
       <c r="N15" s="7" t="s">
@@ -5865,43 +5853,43 @@
       <c r="Q15" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="T15" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U15" s="53" t="s">
+      <c r="T15" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U15" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="V15" s="53" t="s">
+      <c r="V15" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="W15" s="57" t="s">
+      <c r="W15" s="47" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="2:22">
-      <c r="B16" s="21" t="s">
+    <row r="16" spans="2:24">
+      <c r="B16" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="48" t="s">
+      <c r="H16" s="48"/>
+      <c r="I16" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="L16" s="43" t="s">
+      <c r="L16" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="40">
         <v>48</v>
       </c>
       <c r="N16" s="7" t="s">
@@ -5915,42 +5903,42 @@
       <c r="Q16" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="T16" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U16" s="53" t="s">
+      <c r="T16" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U16" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="V16" s="53" t="s">
+      <c r="V16" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="36" t="s">
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="40">
         <v>48</v>
       </c>
       <c r="N17" s="7" t="s">
@@ -5964,39 +5952,39 @@
       <c r="Q17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="T17" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U17" s="53" t="s">
+      <c r="T17" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U17" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="V17" s="53" t="s">
+      <c r="V17" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="2:22">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="48" t="s">
+      <c r="I18" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="K18" s="47" t="s">
+      <c r="K18" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="L18" s="43" t="s">
+      <c r="L18" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="40">
         <v>48</v>
       </c>
       <c r="N18" s="7" t="s">
@@ -6010,39 +5998,39 @@
       <c r="Q18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="T18" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U18" s="53" t="s">
+      <c r="T18" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U18" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="V18" s="53" t="s">
+      <c r="V18" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:22">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="48" t="s">
+      <c r="I19" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="K19" s="47" t="s">
+      <c r="K19" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="L19" s="43" t="s">
+      <c r="L19" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="40">
         <v>48</v>
       </c>
       <c r="N19" s="7" t="s">
@@ -6056,39 +6044,39 @@
       <c r="Q19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="T19" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U19" s="53" t="s">
+      <c r="T19" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U19" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="V19" s="53" t="s">
+      <c r="V19" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="2:22">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="48" t="s">
+      <c r="I20" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="K20" s="47" t="s">
+      <c r="K20" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="L20" s="43" t="s">
+      <c r="L20" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="40">
         <v>48</v>
       </c>
       <c r="N20" s="7" t="s">
@@ -6102,39 +6090,39 @@
       <c r="Q20" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="T20" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U20" s="53" t="s">
+      <c r="T20" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U20" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="V20" s="53" t="s">
+      <c r="V20" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:22">
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="48" t="s">
+      <c r="I21" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="K21" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="L21" s="43" t="s">
+      <c r="L21" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="40">
         <v>48</v>
       </c>
       <c r="N21" s="7" t="s">
@@ -6148,39 +6136,39 @@
       <c r="Q21" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="T21" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U21" s="53" t="s">
+      <c r="T21" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U21" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="V21" s="53" t="s">
+      <c r="V21" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:22">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="48" t="s">
+      <c r="I22" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="K22" s="47" t="s">
+      <c r="K22" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="L22" s="43" t="s">
+      <c r="L22" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="40">
         <v>48</v>
       </c>
       <c r="N22" s="7" t="s">
@@ -6194,39 +6182,39 @@
       <c r="Q22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="T22" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U22" s="53" t="s">
+      <c r="T22" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U22" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="V22" s="53" t="s">
+      <c r="V22" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:22">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="48" t="s">
+      <c r="I23" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="K23" s="47" t="s">
+      <c r="K23" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="43" t="s">
+      <c r="L23" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="40">
         <v>48</v>
       </c>
       <c r="N23" s="7" t="s">
@@ -6240,39 +6228,39 @@
       <c r="Q23" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="T23" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U23" s="53" t="s">
+      <c r="T23" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U23" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="V23" s="53" t="s">
+      <c r="V23" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="2:22">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="48" t="s">
+      <c r="I24" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="K24" s="47" t="s">
+      <c r="K24" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="L24" s="43" t="s">
+      <c r="L24" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="40">
         <v>48</v>
       </c>
       <c r="N24" s="7" t="s">
@@ -6286,39 +6274,39 @@
       <c r="Q24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="T24" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U24" s="53" t="s">
+      <c r="T24" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U24" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="V24" s="53" t="s">
+      <c r="V24" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="2:22">
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="48" t="s">
+      <c r="I25" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="L25" s="43" t="s">
+      <c r="L25" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="40">
         <v>48</v>
       </c>
       <c r="N25" s="7" t="s">
@@ -6332,36 +6320,36 @@
       <c r="Q25" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="T25" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U25" s="53" t="s">
+      <c r="T25" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U25" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="V25" s="53" t="s">
+      <c r="V25" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" spans="2:22">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K26" s="47" t="s">
+      <c r="K26" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="L26" s="43" t="s">
+      <c r="L26" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="40">
         <v>48</v>
       </c>
       <c r="N26" s="7" t="s">
@@ -6375,36 +6363,36 @@
       <c r="Q26" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="T26" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U26" s="53" t="s">
+      <c r="T26" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U26" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="V26" s="53" t="s">
+      <c r="V26" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="2:22">
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="L27" s="43" t="s">
+      <c r="L27" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="40">
         <v>48</v>
       </c>
       <c r="N27" s="7" t="s">
@@ -6418,36 +6406,36 @@
       <c r="Q27" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="T27" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U27" s="53" t="s">
+      <c r="T27" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U27" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="V27" s="53" t="s">
+      <c r="V27" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="2:22">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="L28" s="43" t="s">
+      <c r="L28" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="40">
         <v>48</v>
       </c>
       <c r="N28" s="7" t="s">
@@ -6461,36 +6449,36 @@
       <c r="Q28" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="T28" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U28" s="53" t="s">
+      <c r="T28" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U28" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="V28" s="53" t="s">
+      <c r="V28" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="29" spans="2:22">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K29" s="47" t="s">
+      <c r="K29" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="L29" s="43" t="s">
+      <c r="L29" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N29" s="7" t="s">
@@ -6504,36 +6492,36 @@
       <c r="Q29" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="T29" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="53" t="s">
+      <c r="T29" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U29" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="V29" s="53" t="s">
+      <c r="V29" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="30" spans="2:22">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="K30" s="47" t="s">
+      <c r="K30" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="L30" s="43" t="s">
+      <c r="L30" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M30" s="26" t="s">
+      <c r="M30" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N30" s="7" t="s">
@@ -6547,36 +6535,36 @@
       <c r="Q30" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="T30" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U30" s="53" t="s">
+      <c r="T30" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U30" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="V30" s="53" t="s">
+      <c r="V30" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="2:22">
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="49" t="s">
         <v>224</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="47" t="s">
+      <c r="K31" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="L31" s="43" t="s">
+      <c r="L31" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M31" s="26" t="s">
+      <c r="M31" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N31" s="7" t="s">
@@ -6590,36 +6578,36 @@
       <c r="Q31" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="T31" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U31" s="53" t="s">
+      <c r="T31" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U31" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="V31" s="53" t="s">
+      <c r="V31" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="2:22">
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K32" s="47" t="s">
+      <c r="K32" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="L32" s="43" t="s">
+      <c r="L32" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M32" s="26" t="s">
+      <c r="M32" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N32" s="7" t="s">
@@ -6633,36 +6621,36 @@
       <c r="Q32" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="T32" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U32" s="58" t="s">
+      <c r="T32" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U32" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="V32" s="53" t="s">
+      <c r="V32" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="2:22">
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K33" s="47" t="s">
+      <c r="K33" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="L33" s="43" t="s">
+      <c r="L33" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M33" s="26" t="s">
+      <c r="M33" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N33" s="7" t="s">
@@ -6676,36 +6664,36 @@
       <c r="Q33" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="T33" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U33" s="53" t="s">
+      <c r="T33" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U33" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="V33" s="53" t="s">
+      <c r="V33" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:22">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="K34" s="47" t="s">
+      <c r="K34" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="L34" s="43" t="s">
+      <c r="L34" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M34" s="26" t="s">
+      <c r="M34" s="40" t="s">
         <v>216</v>
       </c>
       <c r="N34" s="7" t="s">
@@ -6719,1132 +6707,1132 @@
       <c r="Q34" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="T34" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U34" s="53" t="s">
+      <c r="T34" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U34" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="V34" s="53" t="s">
+      <c r="V34" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="2:22">
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K35" s="47" t="s">
+      <c r="K35" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="L35" s="43" t="s">
+      <c r="L35" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M35" s="26" t="s">
+      <c r="M35" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="P35" s="44" t="str">
+      <c r="P35" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T35" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U35" s="53" t="s">
+      <c r="T35" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U35" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="V35" s="53" t="s">
+      <c r="V35" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:22">
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="47" t="s">
+      <c r="K36" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="L36" s="43" t="s">
+      <c r="L36" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M36" s="26" t="s">
+      <c r="M36" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P36" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T36" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U36" s="53" t="s">
+      <c r="T36" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U36" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="V36" s="53" t="s">
+      <c r="V36" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="37" spans="2:22">
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K37" s="47" t="s">
+      <c r="K37" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="L37" s="43" t="s">
+      <c r="L37" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M37" s="26" t="s">
+      <c r="M37" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P37" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T37" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U37" s="53" t="s">
+      <c r="T37" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U37" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="V37" s="53" t="s">
+      <c r="V37" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" spans="2:22">
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="K38" s="47" t="s">
+      <c r="K38" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="L38" s="43" t="s">
+      <c r="L38" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M38" s="26" t="s">
+      <c r="M38" s="40" t="s">
         <v>260</v>
       </c>
       <c r="P38" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T38" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U38" s="53" t="s">
+      <c r="T38" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U38" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="V38" s="53" t="s">
+      <c r="V38" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" spans="2:22">
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="L39" s="43" t="s">
+      <c r="L39" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M39" s="26" t="s">
+      <c r="M39" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P39" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T39" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U39" s="53" t="s">
+      <c r="T39" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U39" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="V39" s="53" t="s">
+      <c r="V39" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="2:22">
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="D40" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K40" s="47" t="s">
+      <c r="K40" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="L40" s="43" t="s">
+      <c r="L40" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="M40" s="26" t="s">
+      <c r="M40" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P40" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T40" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U40" s="53" t="s">
+      <c r="T40" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U40" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="V40" s="53" t="s">
+      <c r="V40" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" spans="2:22">
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="33" t="s">
         <v>272</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D41" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K41" s="47" t="s">
+      <c r="K41" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="L41" s="43" t="s">
+      <c r="L41" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M41" s="26" t="s">
+      <c r="M41" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P41" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T41" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U41" s="53" t="s">
+      <c r="T41" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U41" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="V41" s="53" t="s">
+      <c r="V41" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:22">
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K42" s="47" t="s">
+      <c r="K42" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="L42" s="43" t="s">
+      <c r="L42" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M42" s="26" t="s">
+      <c r="M42" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P42" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T42" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U42" s="53" t="s">
+      <c r="T42" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U42" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="V42" s="53" t="s">
+      <c r="V42" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="43" spans="2:22">
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K43" s="47" t="s">
+      <c r="K43" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="L43" s="43" t="s">
+      <c r="L43" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M43" s="26" t="s">
+      <c r="M43" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P43" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T43" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U43" s="53" t="s">
+      <c r="T43" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U43" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="V43" s="53" t="s">
+      <c r="V43" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:22">
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="47" t="s">
+      <c r="K44" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="L44" s="43" t="s">
+      <c r="L44" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M44" s="26" t="s">
+      <c r="M44" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P44" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T44" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U44" s="53" t="s">
+      <c r="T44" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U44" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="V44" s="53" t="s">
+      <c r="V44" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:22">
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="34" t="s">
         <v>290</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K45" s="47" t="s">
+      <c r="K45" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="L45" s="43" t="s">
+      <c r="L45" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M45" s="26" t="s">
+      <c r="M45" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P45" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T45" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U45" s="58" t="s">
+      <c r="T45" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U45" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="V45" s="53" t="s">
+      <c r="V45" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="46" spans="2:22">
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="E46" s="24" t="s">
+      <c r="E46" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K46" s="47" t="s">
+      <c r="K46" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="L46" s="43" t="s">
+      <c r="L46" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M46" s="26" t="s">
+      <c r="M46" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T46" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U46" s="58" t="s">
+      <c r="T46" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U46" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="V46" s="53" t="s">
+      <c r="V46" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="47" spans="2:22">
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K47" s="47" t="s">
+      <c r="K47" s="39" t="s">
         <v>301</v>
       </c>
-      <c r="L47" s="43" t="s">
+      <c r="L47" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M47" s="26" t="s">
+      <c r="M47" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P47" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T47" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U47" s="58" t="s">
+      <c r="T47" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U47" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="V47" s="53" t="s">
+      <c r="V47" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:22">
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K48" s="47" t="s">
+      <c r="K48" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="L48" s="43" t="s">
+      <c r="L48" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M48" s="26" t="s">
+      <c r="M48" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P48" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T48" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U48" s="58" t="s">
+      <c r="T48" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U48" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="V48" s="53" t="s">
+      <c r="V48" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" spans="2:22">
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D49" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="K49" s="47" t="s">
+      <c r="K49" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="L49" s="43" t="s">
+      <c r="L49" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M49" s="26" t="s">
+      <c r="M49" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P49" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T49" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U49" s="58" t="s">
+      <c r="T49" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U49" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="V49" s="53" t="s">
+      <c r="V49" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="2:22">
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="34" t="s">
         <v>312</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="I50" s="28"/>
-      <c r="K50" s="47" t="s">
+      <c r="I50" s="48"/>
+      <c r="K50" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="L50" s="43" t="s">
+      <c r="L50" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M50" s="50" t="s">
+      <c r="M50" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P50" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T50" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U50" s="58" t="s">
+      <c r="T50" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U50" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="V50" s="53" t="s">
+      <c r="V50" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" spans="2:22">
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="28"/>
-      <c r="K51" s="47" t="s">
+      <c r="I51" s="48"/>
+      <c r="K51" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="L51" s="43" t="s">
+      <c r="L51" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M51" s="50" t="s">
+      <c r="M51" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P51" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T51" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U51" s="59" t="s">
+      <c r="T51" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U51" s="53" t="s">
         <v>319</v>
       </c>
-      <c r="V51" s="60" t="s">
+      <c r="V51" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="52" spans="2:22">
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="55" t="s">
         <v>322</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I52" s="28"/>
-      <c r="K52" s="47" t="s">
+      <c r="I52" s="48"/>
+      <c r="K52" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="L52" s="43" t="s">
+      <c r="L52" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="M52" s="50" t="s">
+      <c r="M52" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P52" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T52" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U52" s="59" t="s">
+      <c r="T52" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U52" s="53" t="s">
         <v>324</v>
       </c>
-      <c r="V52" s="60" t="s">
+      <c r="V52" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="53" spans="2:22">
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I53" s="28"/>
-      <c r="K53" s="47" t="s">
+      <c r="I53" s="48"/>
+      <c r="K53" s="39" t="s">
         <v>327</v>
       </c>
-      <c r="L53" s="43" t="s">
+      <c r="L53" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M53" s="50">
+      <c r="M53" s="52">
         <v>48</v>
       </c>
       <c r="P53" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T53" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U53" s="59" t="s">
+      <c r="T53" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U53" s="53" t="s">
         <v>328</v>
       </c>
-      <c r="V53" s="60" t="s">
+      <c r="V53" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="2:22">
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I54" s="28"/>
-      <c r="K54" s="47" t="s">
+      <c r="I54" s="48"/>
+      <c r="K54" s="39" t="s">
         <v>331</v>
       </c>
-      <c r="L54" s="43" t="s">
+      <c r="L54" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M54" s="50">
+      <c r="M54" s="52">
         <v>48</v>
       </c>
       <c r="P54" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T54" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U54" s="59" t="s">
+      <c r="T54" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U54" s="53" t="s">
         <v>332</v>
       </c>
-      <c r="V54" s="60" t="s">
+      <c r="V54" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="55" spans="2:22">
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="D55" s="23" t="s">
+      <c r="D55" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="K55" s="47" t="s">
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="K55" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="L55" s="43" t="s">
+      <c r="L55" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M55" s="50">
+      <c r="M55" s="52">
         <v>48</v>
       </c>
       <c r="P55" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T55" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U55" s="59" t="s">
+      <c r="T55" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U55" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="V55" s="60" t="s">
+      <c r="V55" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="56" spans="2:22">
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="D56" s="23" t="s">
+      <c r="D56" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="K56" s="47" t="s">
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="K56" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="L56" s="43" t="s">
+      <c r="L56" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M56" s="50">
+      <c r="M56" s="52">
         <v>48</v>
       </c>
       <c r="P56" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T56" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U56" s="59" t="s">
+      <c r="T56" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U56" s="53" t="s">
         <v>340</v>
       </c>
-      <c r="V56" s="60" t="s">
+      <c r="V56" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="57" spans="2:22">
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="34" t="s">
         <v>342</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="K57" s="47" t="s">
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="K57" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="L57" s="43" t="s">
+      <c r="L57" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M57" s="50">
+      <c r="M57" s="52">
         <v>48</v>
       </c>
       <c r="P57" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T57" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U57" s="59" t="s">
+      <c r="T57" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U57" s="53" t="s">
         <v>344</v>
       </c>
-      <c r="V57" s="60" t="s">
+      <c r="V57" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58" spans="2:22">
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="33" t="s">
         <v>345</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="C58" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="D58" s="23" t="s">
+      <c r="D58" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="K58" s="47" t="s">
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="K58" s="39" t="s">
         <v>347</v>
       </c>
-      <c r="L58" s="43" t="s">
+      <c r="L58" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M58" s="50">
+      <c r="M58" s="52">
         <v>48</v>
       </c>
       <c r="P58" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T58" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U58" s="59" t="s">
+      <c r="T58" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U58" s="53" t="s">
         <v>348</v>
       </c>
-      <c r="V58" s="60" t="s">
+      <c r="V58" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="59" spans="2:22">
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="34" t="s">
         <v>350</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="E59" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="K59" s="47" t="s">
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="K59" s="39" t="s">
         <v>352</v>
       </c>
-      <c r="L59" s="43" t="s">
+      <c r="L59" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M59" s="50">
+      <c r="M59" s="52">
         <v>48</v>
       </c>
       <c r="P59" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T59" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U59" s="59" t="s">
+      <c r="T59" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U59" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="V59" s="60" t="s">
+      <c r="V59" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="60" spans="2:22">
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="33" t="s">
         <v>354</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="K60" s="47" t="s">
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="K60" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="L60" s="43" t="s">
+      <c r="L60" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M60" s="26" t="s">
+      <c r="M60" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P60" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T60" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U60" s="59" t="s">
+      <c r="T60" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U60" s="53" t="s">
         <v>357</v>
       </c>
-      <c r="V60" s="60" t="s">
+      <c r="V60" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="61" spans="2:22">
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="56" t="s">
         <v>358</v>
       </c>
-      <c r="C61" s="33" t="s">
+      <c r="C61" s="57" t="s">
         <v>359</v>
       </c>
-      <c r="D61" s="31" t="s">
+      <c r="D61" s="55" t="s">
         <v>169</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="K61" s="47" t="s">
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="K61" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="L61" s="43" t="s">
+      <c r="L61" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M61" s="26" t="s">
+      <c r="M61" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P61" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T61" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U61" s="59" t="s">
+      <c r="T61" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U61" s="53" t="s">
         <v>361</v>
       </c>
-      <c r="V61" s="60" t="s">
+      <c r="V61" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="62" spans="2:22">
-      <c r="B62" s="32" t="s">
+      <c r="B62" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="58" t="s">
         <v>363</v>
       </c>
-      <c r="D62" s="35" t="s">
+      <c r="D62" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="E62" s="36" t="s">
+      <c r="E62" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28"/>
-      <c r="K62" s="47" t="s">
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="K62" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="L62" s="43" t="s">
+      <c r="L62" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M62" s="26" t="s">
+      <c r="M62" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P62" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T62" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U62" s="59" t="s">
+      <c r="T62" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U62" s="53" t="s">
         <v>366</v>
       </c>
-      <c r="V62" s="60" t="s">
+      <c r="V62" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="63" spans="2:22">
-      <c r="B63" s="37" t="s">
+      <c r="B63" s="60" t="s">
         <v>367</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="49" t="s">
         <v>368</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="50" t="s">
         <v>368</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="K63" s="47" t="s">
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="K63" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="L63" s="43" t="s">
+      <c r="L63" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M63" s="26" t="s">
+      <c r="M63" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P63" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T63" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U63" s="59" t="s">
+      <c r="T63" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U63" s="53" t="s">
         <v>370</v>
       </c>
-      <c r="V63" s="60" t="s">
+      <c r="V63" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="64" spans="2:22">
-      <c r="B64" s="37" t="s">
+      <c r="B64" s="60" t="s">
         <v>371</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="D64" s="23" t="s">
+      <c r="D64" s="35" t="s">
         <v>373</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="K64" s="47" t="s">
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="K64" s="39" t="s">
         <v>374</v>
       </c>
-      <c r="L64" s="43" t="s">
+      <c r="L64" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M64" s="26" t="s">
+      <c r="M64" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P64" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T64" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U64" s="59" t="s">
+      <c r="T64" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U64" s="53" t="s">
         <v>375</v>
       </c>
-      <c r="V64" s="60" t="s">
+      <c r="V64" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -7852,44 +7840,44 @@
       <c r="B65" s="61" t="s">
         <v>376</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="49" t="s">
         <v>377</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D65" s="50" t="s">
         <v>377</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="28"/>
-      <c r="K65" s="47" t="s">
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="K65" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="L65" s="43" t="s">
+      <c r="L65" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M65" s="26" t="s">
+      <c r="M65" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P65" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T65" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U65" s="59" t="s">
+      <c r="T65" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U65" s="53" t="s">
         <v>379</v>
       </c>
-      <c r="V65" s="60" t="s">
+      <c r="V65" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="66" spans="2:22">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="33" t="s">
         <v>380</v>
       </c>
       <c r="C66" s="62" t="s">
@@ -7898,38 +7886,38 @@
       <c r="D66" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
-      <c r="K66" s="47" t="s">
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="K66" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="L66" s="43" t="s">
+      <c r="L66" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M66" s="26">
+      <c r="M66" s="40">
         <v>48</v>
       </c>
       <c r="P66" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T66" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U66" s="59" t="s">
+      <c r="T66" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U66" s="53" t="s">
         <v>383</v>
       </c>
-      <c r="V66" s="60" t="s">
+      <c r="V66" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="67" spans="2:22">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="33" t="s">
         <v>384</v>
       </c>
       <c r="C67" s="3" t="s">
@@ -7941,28 +7929,28 @@
       <c r="E67" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="K67" s="47" t="s">
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="K67" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="L67" s="43" t="s">
+      <c r="L67" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M67" s="26">
+      <c r="M67" s="40">
         <v>48</v>
       </c>
       <c r="P67" s="8" t="str">
         <f t="shared" ref="P67:P130" si="1">N67&amp;O67</f>
         <v/>
       </c>
-      <c r="T67" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U67" s="59" t="s">
+      <c r="T67" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U67" s="53" t="s">
         <v>387</v>
       </c>
-      <c r="V67" s="60" t="s">
+      <c r="V67" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -7977,28 +7965,28 @@
       <c r="E68" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="K68" s="47" t="s">
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="K68" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="L68" s="43" t="s">
+      <c r="L68" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M68" s="26">
+      <c r="M68" s="40">
         <v>48</v>
       </c>
       <c r="P68" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T68" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U68" s="59" t="s">
+      <c r="T68" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U68" s="53" t="s">
         <v>390</v>
       </c>
-      <c r="V68" s="60" t="s">
+      <c r="V68" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8013,27 +8001,27 @@
       <c r="E69" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="I69" s="28"/>
-      <c r="K69" s="47" t="s">
+      <c r="I69" s="48"/>
+      <c r="K69" s="39" t="s">
         <v>392</v>
       </c>
-      <c r="L69" s="43" t="s">
+      <c r="L69" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M69" s="26">
+      <c r="M69" s="40">
         <v>48</v>
       </c>
       <c r="P69" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T69" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U69" s="59" t="s">
+      <c r="T69" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U69" s="53" t="s">
         <v>393</v>
       </c>
-      <c r="V69" s="60" t="s">
+      <c r="V69" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8041,7 +8029,7 @@
       <c r="B70" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C70" s="33" t="s">
+      <c r="C70" s="57" t="s">
         <v>395</v>
       </c>
       <c r="D70" s="66" t="s">
@@ -8050,32 +8038,32 @@
       <c r="E70" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I70" s="28"/>
-      <c r="K70" s="47" t="s">
+      <c r="I70" s="48"/>
+      <c r="K70" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="L70" s="43" t="s">
+      <c r="L70" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M70" s="26">
+      <c r="M70" s="40">
         <v>48</v>
       </c>
       <c r="P70" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T70" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U70" s="59" t="s">
+      <c r="T70" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U70" s="53" t="s">
         <v>397</v>
       </c>
-      <c r="V70" s="60" t="s">
+      <c r="V70" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="71" spans="2:22">
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="56" t="s">
         <v>398</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -8087,27 +8075,27 @@
       <c r="E71" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I71" s="28"/>
-      <c r="K71" s="47" t="s">
+      <c r="I71" s="48"/>
+      <c r="K71" s="39" t="s">
         <v>400</v>
       </c>
-      <c r="L71" s="43" t="s">
+      <c r="L71" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M71" s="26">
+      <c r="M71" s="40">
         <v>48</v>
       </c>
       <c r="P71" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T71" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U71" s="59" t="s">
+      <c r="T71" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U71" s="53" t="s">
         <v>401</v>
       </c>
-      <c r="V71" s="60" t="s">
+      <c r="V71" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8122,32 +8110,32 @@
       <c r="E72" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="I72" s="28"/>
-      <c r="K72" s="47" t="s">
+      <c r="I72" s="48"/>
+      <c r="K72" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="L72" s="43" t="s">
+      <c r="L72" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M72" s="26">
+      <c r="M72" s="40">
         <v>48</v>
       </c>
       <c r="P72" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T72" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U72" s="59" t="s">
+      <c r="T72" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U72" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="V72" s="60" t="s">
+      <c r="V72" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="73" spans="2:22">
-      <c r="B73" s="32"/>
+      <c r="B73" s="56"/>
       <c r="C73" s="65" t="s">
         <v>405</v>
       </c>
@@ -8157,27 +8145,27 @@
       <c r="E73" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="I73" s="28"/>
-      <c r="K73" s="47" t="s">
+      <c r="I73" s="48"/>
+      <c r="K73" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="L73" s="43" t="s">
+      <c r="L73" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M73" s="26">
+      <c r="M73" s="40">
         <v>48</v>
       </c>
       <c r="P73" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T73" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U73" s="59" t="s">
+      <c r="T73" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U73" s="53" t="s">
         <v>407</v>
       </c>
-      <c r="V73" s="60" t="s">
+      <c r="V73" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8192,31 +8180,31 @@
       <c r="E74" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="K74" s="47" t="s">
+      <c r="K74" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="L74" s="43" t="s">
+      <c r="L74" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M74" s="26">
+      <c r="M74" s="40">
         <v>48</v>
       </c>
       <c r="P74" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T74" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U74" s="59" t="s">
+      <c r="T74" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U74" s="53" t="s">
         <v>410</v>
       </c>
-      <c r="V74" s="60" t="s">
+      <c r="V74" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="75" spans="2:22">
-      <c r="B75" s="32"/>
+      <c r="B75" s="56"/>
       <c r="C75" s="65" t="s">
         <v>411</v>
       </c>
@@ -8226,94 +8214,94 @@
       <c r="E75" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="K75" s="47" t="s">
+      <c r="K75" s="39" t="s">
         <v>412</v>
       </c>
-      <c r="L75" s="43" t="s">
+      <c r="L75" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M75" s="26">
+      <c r="M75" s="40">
         <v>48</v>
       </c>
       <c r="P75" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T75" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U75" s="59" t="s">
+      <c r="T75" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U75" s="53" t="s">
         <v>413</v>
       </c>
-      <c r="V75" s="60" t="s">
+      <c r="V75" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="76" spans="2:22">
-      <c r="B76" s="21"/>
-      <c r="C76" s="33" t="s">
+      <c r="B76" s="33"/>
+      <c r="C76" s="57" t="s">
         <v>414</v>
       </c>
-      <c r="D76" s="31" t="s">
+      <c r="D76" s="55" t="s">
         <v>209</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K76" s="47" t="s">
+      <c r="K76" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="L76" s="43" t="s">
+      <c r="L76" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M76" s="26">
+      <c r="M76" s="40">
         <v>48</v>
       </c>
       <c r="P76" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T76" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U76" s="59" t="s">
+      <c r="T76" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U76" s="53" t="s">
         <v>416</v>
       </c>
-      <c r="V76" s="60" t="s">
+      <c r="V76" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="77" spans="2:22">
-      <c r="B77" s="32"/>
-      <c r="C77" s="33" t="s">
+      <c r="B77" s="56"/>
+      <c r="C77" s="57" t="s">
         <v>417</v>
       </c>
-      <c r="D77" s="31" t="s">
+      <c r="D77" s="55" t="s">
         <v>209</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K77" s="47" t="s">
+      <c r="K77" s="39" t="s">
         <v>418</v>
       </c>
-      <c r="L77" s="43" t="s">
+      <c r="L77" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M77" s="26">
+      <c r="M77" s="40">
         <v>48</v>
       </c>
       <c r="P77" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T77" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U77" s="59" t="s">
+      <c r="T77" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U77" s="53" t="s">
         <v>419</v>
       </c>
-      <c r="V77" s="60" t="s">
+      <c r="V77" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8328,65 +8316,65 @@
       <c r="E78" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="K78" s="47" t="s">
+      <c r="K78" s="39" t="s">
         <v>421</v>
       </c>
-      <c r="L78" s="43" t="s">
+      <c r="L78" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="M78" s="26">
+      <c r="M78" s="40">
         <v>48</v>
       </c>
       <c r="P78" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T78" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U78" s="59" t="s">
+      <c r="T78" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U78" s="53" t="s">
         <v>422</v>
       </c>
-      <c r="V78" s="60" t="s">
+      <c r="V78" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="79" spans="2:22">
-      <c r="B79" s="32"/>
-      <c r="C79" s="33" t="s">
+      <c r="B79" s="56"/>
+      <c r="C79" s="57" t="s">
         <v>423</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="55" t="s">
         <v>423</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K79" s="47" t="s">
+      <c r="K79" s="39" t="s">
         <v>424</v>
       </c>
-      <c r="L79" s="43" t="s">
+      <c r="L79" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M79" s="26">
+      <c r="M79" s="40">
         <v>48</v>
       </c>
       <c r="P79" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T79" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U79" s="59" t="s">
+      <c r="T79" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U79" s="53" t="s">
         <v>425</v>
       </c>
-      <c r="V79" s="60" t="s">
+      <c r="V79" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="80" spans="2:22">
-      <c r="B80" s="32"/>
+      <c r="B80" s="56"/>
       <c r="C80" s="65" t="s">
         <v>426</v>
       </c>
@@ -8396,128 +8384,128 @@
       <c r="E80" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K80" s="47" t="s">
+      <c r="K80" s="39" t="s">
         <v>427</v>
       </c>
-      <c r="L80" s="43" t="s">
+      <c r="L80" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M80" s="26">
+      <c r="M80" s="40">
         <v>48</v>
       </c>
       <c r="P80" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T80" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U80" s="59" t="s">
+      <c r="T80" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U80" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="V80" s="60" t="s">
+      <c r="V80" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="81" spans="2:22">
-      <c r="B81" s="32"/>
-      <c r="C81" s="33" t="s">
+      <c r="B81" s="56"/>
+      <c r="C81" s="57" t="s">
         <v>429</v>
       </c>
-      <c r="D81" s="31" t="s">
+      <c r="D81" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K81" s="47" t="s">
+      <c r="K81" s="39" t="s">
         <v>430</v>
       </c>
-      <c r="L81" s="43" t="s">
+      <c r="L81" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M81" s="26">
+      <c r="M81" s="40">
         <v>48</v>
       </c>
       <c r="P81" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T81" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U81" s="59" t="s">
+      <c r="T81" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U81" s="53" t="s">
         <v>431</v>
       </c>
-      <c r="V81" s="60" t="s">
+      <c r="V81" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="82" spans="2:22">
-      <c r="B82" s="32"/>
-      <c r="C82" s="22" t="s">
+      <c r="B82" s="56"/>
+      <c r="C82" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="D82" s="31" t="s">
+      <c r="D82" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="K82" s="47" t="s">
+      <c r="K82" s="39" t="s">
         <v>433</v>
       </c>
-      <c r="L82" s="43" t="s">
+      <c r="L82" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M82" s="26">
+      <c r="M82" s="40">
         <v>48</v>
       </c>
       <c r="P82" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T82" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U82" s="59" t="s">
+      <c r="T82" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U82" s="53" t="s">
         <v>434</v>
       </c>
-      <c r="V82" s="60" t="s">
+      <c r="V82" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="83" spans="2:22">
       <c r="B83" s="64"/>
-      <c r="C83" s="33" t="s">
+      <c r="C83" s="57" t="s">
         <v>435</v>
       </c>
-      <c r="D83" s="31" t="s">
+      <c r="D83" s="55" t="s">
         <v>147</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K83" s="47" t="s">
+      <c r="K83" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="43" t="s">
+      <c r="L83" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M83" s="26">
+      <c r="M83" s="40">
         <v>48</v>
       </c>
       <c r="P83" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T83" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U83" s="59" t="s">
+      <c r="T83" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U83" s="53" t="s">
         <v>437</v>
       </c>
-      <c r="V83" s="60" t="s">
+      <c r="V83" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8534,128 +8522,128 @@
       <c r="E84" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K84" s="47" t="s">
+      <c r="K84" s="39" t="s">
         <v>440</v>
       </c>
-      <c r="L84" s="43" t="s">
+      <c r="L84" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M84" s="26">
+      <c r="M84" s="40">
         <v>48</v>
       </c>
       <c r="P84" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T84" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U84" s="59" t="s">
+      <c r="T84" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U84" s="53" t="s">
         <v>441</v>
       </c>
-      <c r="V84" s="60" t="s">
+      <c r="V84" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="85" spans="2:22">
       <c r="B85" s="68"/>
-      <c r="C85" s="33" t="s">
+      <c r="C85" s="57" t="s">
         <v>442</v>
       </c>
-      <c r="D85" s="31" t="s">
+      <c r="D85" s="55" t="s">
         <v>186</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K85" s="47" t="s">
+      <c r="K85" s="39" t="s">
         <v>443</v>
       </c>
-      <c r="L85" s="43" t="s">
+      <c r="L85" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M85" s="26">
+      <c r="M85" s="40">
         <v>48</v>
       </c>
       <c r="P85" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T85" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U85" s="59" t="s">
+      <c r="T85" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U85" s="53" t="s">
         <v>444</v>
       </c>
-      <c r="V85" s="60" t="s">
+      <c r="V85" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="86" spans="2:22">
       <c r="B86" s="68"/>
-      <c r="C86" s="33" t="s">
+      <c r="C86" s="57" t="s">
         <v>445</v>
       </c>
-      <c r="D86" s="31" t="s">
+      <c r="D86" s="55" t="s">
         <v>83</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K86" s="47" t="s">
+      <c r="K86" s="39" t="s">
         <v>446</v>
       </c>
-      <c r="L86" s="43" t="s">
+      <c r="L86" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M86" s="26">
+      <c r="M86" s="40">
         <v>48</v>
       </c>
       <c r="P86" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T86" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U86" s="81" t="s">
+      <c r="T86" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U86" s="69" t="s">
         <v>447</v>
       </c>
-      <c r="V86" s="60" t="s">
+      <c r="V86" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="87" spans="2:22">
       <c r="B87" s="68"/>
-      <c r="C87" s="33" t="s">
+      <c r="C87" s="57" t="s">
         <v>448</v>
       </c>
-      <c r="D87" s="31" t="s">
+      <c r="D87" s="55" t="s">
         <v>448</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K87" s="47" t="s">
+      <c r="K87" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="L87" s="43" t="s">
+      <c r="L87" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M87" s="26">
+      <c r="M87" s="40">
         <v>48</v>
       </c>
       <c r="P87" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T87" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U87" s="59" t="s">
+      <c r="T87" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U87" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="V87" s="60" t="s">
+      <c r="V87" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8670,26 +8658,26 @@
       <c r="E88" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="K88" s="47" t="s">
+      <c r="K88" s="39" t="s">
         <v>452</v>
       </c>
-      <c r="L88" s="43" t="s">
+      <c r="L88" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M88" s="26">
+      <c r="M88" s="40">
         <v>48</v>
       </c>
       <c r="P88" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T88" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U88" s="82" t="s">
+      <c r="T88" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U88" s="70" t="s">
         <v>453</v>
       </c>
-      <c r="V88" s="60" t="s">
+      <c r="V88" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8704,26 +8692,26 @@
       <c r="E89" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K89" s="47" t="s">
+      <c r="K89" s="39" t="s">
         <v>455</v>
       </c>
-      <c r="L89" s="43" t="s">
+      <c r="L89" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M89" s="26">
+      <c r="M89" s="40">
         <v>48</v>
       </c>
       <c r="P89" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T89" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U89" s="82" t="s">
+      <c r="T89" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U89" s="70" t="s">
         <v>456</v>
       </c>
-      <c r="V89" s="60" t="s">
+      <c r="V89" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8738,26 +8726,26 @@
       <c r="E90" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K90" s="47" t="s">
+      <c r="K90" s="39" t="s">
         <v>459</v>
       </c>
-      <c r="L90" s="43" t="s">
+      <c r="L90" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M90" s="26">
+      <c r="M90" s="40">
         <v>48</v>
       </c>
       <c r="P90" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T90" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U90" s="82" t="s">
+      <c r="T90" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U90" s="70" t="s">
         <v>460</v>
       </c>
-      <c r="V90" s="60" t="s">
+      <c r="V90" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8772,94 +8760,94 @@
       <c r="E91" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K91" s="47" t="s">
+      <c r="K91" s="39" t="s">
         <v>462</v>
       </c>
-      <c r="L91" s="43" t="s">
+      <c r="L91" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M91" s="26">
+      <c r="M91" s="40">
         <v>48</v>
       </c>
       <c r="P91" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T91" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U91" s="82" t="s">
+      <c r="T91" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U91" s="70" t="s">
         <v>463</v>
       </c>
-      <c r="V91" s="60" t="s">
+      <c r="V91" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="92" spans="2:22">
       <c r="B92" s="61"/>
-      <c r="C92" s="33" t="s">
+      <c r="C92" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="D92" s="31" t="s">
+      <c r="D92" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K92" s="47" t="s">
+      <c r="K92" s="39" t="s">
         <v>465</v>
       </c>
-      <c r="L92" s="43" t="s">
+      <c r="L92" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M92" s="26">
+      <c r="M92" s="40">
         <v>48</v>
       </c>
       <c r="P92" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T92" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U92" s="82" t="s">
+      <c r="T92" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U92" s="70" t="s">
         <v>466</v>
       </c>
-      <c r="V92" s="60" t="s">
+      <c r="V92" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="93" spans="2:22">
       <c r="B93" s="68"/>
-      <c r="C93" s="33" t="s">
+      <c r="C93" s="57" t="s">
         <v>467</v>
       </c>
-      <c r="D93" s="31" t="s">
+      <c r="D93" s="55" t="s">
         <v>173</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K93" s="47" t="s">
+      <c r="K93" s="39" t="s">
         <v>468</v>
       </c>
-      <c r="L93" s="43" t="s">
+      <c r="L93" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M93" s="26">
+      <c r="M93" s="40">
         <v>48</v>
       </c>
       <c r="P93" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T93" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U93" s="82" t="s">
+      <c r="T93" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U93" s="70" t="s">
         <v>469</v>
       </c>
-      <c r="V93" s="60" t="s">
+      <c r="V93" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8876,60 +8864,60 @@
       <c r="E94" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K94" s="47" t="s">
+      <c r="K94" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="L94" s="43" t="s">
+      <c r="L94" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M94" s="26">
+      <c r="M94" s="40">
         <v>48</v>
       </c>
       <c r="P94" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T94" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U94" s="82" t="s">
+      <c r="T94" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U94" s="70" t="s">
         <v>474</v>
       </c>
-      <c r="V94" s="60" t="s">
+      <c r="V94" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="95" spans="2:22">
       <c r="B95" s="68"/>
-      <c r="C95" s="33" t="s">
+      <c r="C95" s="57" t="s">
         <v>475</v>
       </c>
-      <c r="D95" s="31" t="s">
+      <c r="D95" s="55" t="s">
         <v>186</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K95" s="47" t="s">
+      <c r="K95" s="39" t="s">
         <v>476</v>
       </c>
-      <c r="L95" s="43" t="s">
+      <c r="L95" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M95" s="26">
+      <c r="M95" s="40">
         <v>48</v>
       </c>
       <c r="P95" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T95" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U95" s="82" t="s">
+      <c r="T95" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U95" s="70" t="s">
         <v>477</v>
       </c>
-      <c r="V95" s="60" t="s">
+      <c r="V95" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8944,61 +8932,61 @@
       <c r="E96" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="K96" s="47" t="s">
+      <c r="K96" s="39" t="s">
         <v>480</v>
       </c>
-      <c r="L96" s="43" t="s">
+      <c r="L96" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M96" s="26">
+      <c r="M96" s="40">
         <v>48</v>
       </c>
       <c r="P96" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T96" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U96" s="59" t="s">
+      <c r="T96" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U96" s="53" t="s">
         <v>481</v>
       </c>
-      <c r="V96" s="60" t="s">
+      <c r="V96" s="54" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="97" spans="2:22">
       <c r="B97" s="61"/>
-      <c r="C97" s="33" t="s">
+      <c r="C97" s="57" t="s">
         <v>482</v>
       </c>
-      <c r="D97" s="31" t="s">
+      <c r="D97" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="I97" s="28"/>
-      <c r="K97" s="47" t="s">
+      <c r="I97" s="48"/>
+      <c r="K97" s="39" t="s">
         <v>483</v>
       </c>
-      <c r="L97" s="43" t="s">
+      <c r="L97" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M97" s="26">
+      <c r="M97" s="40">
         <v>48</v>
       </c>
       <c r="P97" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T97" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U97" s="59" t="s">
+      <c r="T97" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U97" s="53" t="s">
         <v>484</v>
       </c>
-      <c r="V97" s="60" t="s">
+      <c r="V97" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9013,61 +9001,61 @@
       <c r="E98" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="I98" s="28"/>
-      <c r="K98" s="47" t="s">
+      <c r="I98" s="48"/>
+      <c r="K98" s="39" t="s">
         <v>486</v>
       </c>
-      <c r="L98" s="43" t="s">
+      <c r="L98" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M98" s="26">
+      <c r="M98" s="40">
         <v>48</v>
       </c>
       <c r="P98" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T98" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U98" s="59" t="s">
+      <c r="T98" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U98" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="V98" s="60" t="s">
+      <c r="V98" s="54" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="99" spans="3:22">
-      <c r="C99" s="33" t="s">
+    <row r="99" spans="2:22">
+      <c r="C99" s="57" t="s">
         <v>322</v>
       </c>
-      <c r="D99" s="31" t="s">
+      <c r="D99" s="55" t="s">
         <v>322</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I99" s="28"/>
-      <c r="K99" s="47" t="s">
+      <c r="I99" s="48"/>
+      <c r="K99" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="L99" s="43" t="s">
+      <c r="L99" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M99" s="26">
+      <c r="M99" s="40">
         <v>48</v>
       </c>
       <c r="P99" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T99" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U99" s="82" t="s">
+      <c r="T99" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U99" s="70" t="s">
         <v>489</v>
       </c>
-      <c r="V99" s="60" t="s">
+      <c r="V99" s="54" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9082,28 +9070,28 @@
       <c r="E100" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="28"/>
-      <c r="K100" s="47" t="s">
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="K100" s="39" t="s">
         <v>491</v>
       </c>
-      <c r="L100" s="43" t="s">
+      <c r="L100" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M100" s="26">
+      <c r="M100" s="40">
         <v>48</v>
       </c>
       <c r="P100" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T100" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U100" s="59" t="s">
+      <c r="T100" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U100" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="V100" s="60" t="s">
+      <c r="V100" s="54" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9116,68 +9104,68 @@
       <c r="E101" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="28"/>
-      <c r="K101" s="47" t="s">
+      <c r="F101" s="45"/>
+      <c r="G101" s="45"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
+      <c r="K101" s="39" t="s">
         <v>494</v>
       </c>
-      <c r="L101" s="43" t="s">
+      <c r="L101" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M101" s="26">
+      <c r="M101" s="40">
         <v>48</v>
       </c>
       <c r="P101" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T101" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U101" s="59" t="s">
+      <c r="T101" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U101" s="53" t="s">
         <v>495</v>
       </c>
-      <c r="V101" s="60" t="s">
+      <c r="V101" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="102" spans="2:22">
       <c r="B102" s="68"/>
-      <c r="C102" s="33" t="s">
+      <c r="C102" s="57" t="s">
         <v>496</v>
       </c>
-      <c r="D102" s="31" t="s">
+      <c r="D102" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="28"/>
-      <c r="K102" s="47" t="s">
+      <c r="F102" s="45"/>
+      <c r="G102" s="45"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="K102" s="39" t="s">
         <v>497</v>
       </c>
-      <c r="L102" s="43" t="s">
+      <c r="L102" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M102" s="26">
+      <c r="M102" s="40">
         <v>48</v>
       </c>
       <c r="P102" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T102" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U102" s="59" t="s">
+      <c r="T102" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U102" s="53" t="s">
         <v>498</v>
       </c>
-      <c r="V102" s="60" t="s">
+      <c r="V102" s="54" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9192,30 +9180,30 @@
       <c r="E103" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="28"/>
-      <c r="K103" s="47" t="s">
+      <c r="F103" s="45"/>
+      <c r="G103" s="45"/>
+      <c r="H103" s="48"/>
+      <c r="I103" s="48"/>
+      <c r="K103" s="39" t="s">
         <v>500</v>
       </c>
-      <c r="L103" s="43" t="s">
+      <c r="L103" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M103" s="26">
+      <c r="M103" s="40">
         <v>48</v>
       </c>
       <c r="P103" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T103" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U103" s="59" t="s">
+      <c r="T103" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U103" s="53" t="s">
         <v>501</v>
       </c>
-      <c r="V103" s="60" t="s">
+      <c r="V103" s="54" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9230,30 +9218,30 @@
       <c r="E104" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="28"/>
-      <c r="K104" s="47" t="s">
+      <c r="F104" s="45"/>
+      <c r="G104" s="45"/>
+      <c r="H104" s="48"/>
+      <c r="I104" s="48"/>
+      <c r="K104" s="39" t="s">
         <v>503</v>
       </c>
-      <c r="L104" s="43" t="s">
+      <c r="L104" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M104" s="26">
+      <c r="M104" s="40">
         <v>48</v>
       </c>
       <c r="P104" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T104" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U104" s="59" t="s">
+      <c r="T104" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U104" s="53" t="s">
         <v>504</v>
       </c>
-      <c r="V104" s="60" t="s">
+      <c r="V104" s="54" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9268,133 +9256,133 @@
       <c r="E105" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="F105" s="27"/>
-      <c r="G105" s="27"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="28"/>
-      <c r="K105" s="47" t="s">
+      <c r="F105" s="45"/>
+      <c r="G105" s="45"/>
+      <c r="H105" s="48"/>
+      <c r="I105" s="48"/>
+      <c r="K105" s="39" t="s">
         <v>506</v>
       </c>
-      <c r="L105" s="43" t="s">
+      <c r="L105" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M105" s="26" t="s">
+      <c r="M105" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P105" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T105" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U105" s="59" t="s">
+      <c r="T105" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U105" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="V105" s="60" t="s">
+      <c r="V105" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="3:22">
-      <c r="C106" s="69" t="s">
+    <row r="106" spans="2:22">
+      <c r="C106" s="71" t="s">
         <v>509</v>
       </c>
-      <c r="D106" s="70" t="s">
+      <c r="D106" s="72" t="s">
         <v>510</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="K106" s="47" t="s">
+      <c r="K106" s="39" t="s">
         <v>511</v>
       </c>
-      <c r="L106" s="43" t="s">
+      <c r="L106" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M106" s="26" t="s">
+      <c r="M106" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P106" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T106" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U106" s="59" t="s">
+      <c r="T106" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U106" s="53" t="s">
         <v>512</v>
       </c>
-      <c r="V106" s="60" t="s">
+      <c r="V106" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="3:22">
-      <c r="C107" s="71" t="s">
+    <row r="107" spans="2:22">
+      <c r="C107" s="73" t="s">
         <v>513</v>
       </c>
-      <c r="D107" s="72" t="s">
+      <c r="D107" s="74" t="s">
         <v>364</v>
       </c>
-      <c r="E107" s="26" t="s">
+      <c r="E107" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="K107" s="47" t="s">
+      <c r="K107" s="39" t="s">
         <v>514</v>
       </c>
-      <c r="L107" s="43" t="s">
+      <c r="L107" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M107" s="26" t="s">
+      <c r="M107" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P107" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T107" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U107" s="59" t="s">
+      <c r="T107" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U107" s="53" t="s">
         <v>515</v>
       </c>
-      <c r="V107" s="60" t="s">
+      <c r="V107" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="3:22">
+    <row r="108" spans="2:22">
       <c r="C108" s="8" t="s">
         <v>516</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E108" s="24" t="s">
+      <c r="E108" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="K108" s="47" t="s">
+      <c r="K108" s="39" t="s">
         <v>517</v>
       </c>
-      <c r="L108" s="43" t="s">
+      <c r="L108" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M108" s="26" t="s">
+      <c r="M108" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P108" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T108" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U108" s="59" t="s">
+      <c r="T108" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U108" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="V108" s="60" t="s">
+      <c r="V108" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="3:22">
+    <row r="109" spans="2:22">
       <c r="C109" s="8" t="s">
         <v>519</v>
       </c>
@@ -9404,30 +9392,30 @@
       <c r="E109" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K109" s="47" t="s">
+      <c r="K109" s="39" t="s">
         <v>520</v>
       </c>
-      <c r="L109" s="43" t="s">
+      <c r="L109" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M109" s="26" t="s">
+      <c r="M109" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P109" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T109" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U109" s="59" t="s">
+      <c r="T109" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U109" s="53" t="s">
         <v>521</v>
       </c>
-      <c r="V109" s="60" t="s">
+      <c r="V109" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="3:22">
+    <row r="110" spans="2:22">
       <c r="C110" s="8" t="s">
         <v>522</v>
       </c>
@@ -9437,30 +9425,30 @@
       <c r="E110" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K110" s="47" t="s">
+      <c r="K110" s="39" t="s">
         <v>523</v>
       </c>
-      <c r="L110" s="43" t="s">
+      <c r="L110" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M110" s="26" t="s">
+      <c r="M110" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P110" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T110" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U110" s="59" t="s">
+      <c r="T110" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U110" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="V110" s="60" t="s">
+      <c r="V110" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="3:22">
+    <row r="111" spans="2:22">
       <c r="C111" s="8" t="s">
         <v>525</v>
       </c>
@@ -9470,30 +9458,30 @@
       <c r="E111" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K111" s="47" t="s">
+      <c r="K111" s="39" t="s">
         <v>526</v>
       </c>
-      <c r="L111" s="43" t="s">
+      <c r="L111" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M111" s="26" t="s">
+      <c r="M111" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P111" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T111" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U111" s="59" t="s">
+      <c r="T111" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U111" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="V111" s="60" t="s">
+      <c r="V111" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="3:22">
+    <row r="112" spans="2:22">
       <c r="C112" s="8" t="s">
         <v>528</v>
       </c>
@@ -9503,63 +9491,63 @@
       <c r="E112" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K112" s="47" t="s">
+      <c r="K112" s="39" t="s">
         <v>530</v>
       </c>
-      <c r="L112" s="43" t="s">
+      <c r="L112" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M112" s="26" t="s">
+      <c r="M112" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P112" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T112" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U112" s="59" t="s">
+      <c r="T112" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U112" s="53" t="s">
         <v>531</v>
       </c>
-      <c r="V112" s="60" t="s">
+      <c r="V112" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="3:22">
+    <row r="113" spans="2:22">
       <c r="C113" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="D113" s="23" t="s">
+      <c r="D113" s="35" t="s">
         <v>351</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K113" s="47" t="s">
+      <c r="K113" s="39" t="s">
         <v>533</v>
       </c>
-      <c r="L113" s="43" t="s">
+      <c r="L113" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M113" s="26" t="s">
+      <c r="M113" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P113" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T113" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U113" s="59" t="s">
+      <c r="T113" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U113" s="53" t="s">
         <v>534</v>
       </c>
-      <c r="V113" s="60" t="s">
+      <c r="V113" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="3:22">
+    <row r="114" spans="2:22">
       <c r="C114" s="8" t="s">
         <v>535</v>
       </c>
@@ -9569,30 +9557,30 @@
       <c r="E114" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K114" s="47" t="s">
+      <c r="K114" s="39" t="s">
         <v>536</v>
       </c>
-      <c r="L114" s="43" t="s">
+      <c r="L114" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M114" s="26" t="s">
+      <c r="M114" s="40" t="s">
         <v>260</v>
       </c>
       <c r="P114" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T114" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U114" s="59" t="s">
+      <c r="T114" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U114" s="53" t="s">
         <v>537</v>
       </c>
-      <c r="V114" s="60" t="s">
+      <c r="V114" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="3:22">
+    <row r="115" spans="2:22">
       <c r="C115" s="8" t="s">
         <v>538</v>
       </c>
@@ -9602,30 +9590,30 @@
       <c r="E115" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K115" s="47" t="s">
+      <c r="K115" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="L115" s="43" t="s">
+      <c r="L115" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M115" s="26" t="s">
+      <c r="M115" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P115" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T115" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U115" s="59" t="s">
+      <c r="T115" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U115" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="V115" s="60" t="s">
+      <c r="V115" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="3:22">
+    <row r="116" spans="2:22">
       <c r="C116" s="8" t="s">
         <v>541</v>
       </c>
@@ -9635,30 +9623,30 @@
       <c r="E116" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K116" s="47" t="s">
+      <c r="K116" s="39" t="s">
         <v>542</v>
       </c>
-      <c r="L116" s="43" t="s">
+      <c r="L116" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="M116" s="26" t="s">
+      <c r="M116" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P116" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T116" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U116" s="59" t="s">
+      <c r="T116" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U116" s="53" t="s">
         <v>543</v>
       </c>
-      <c r="V116" s="60" t="s">
+      <c r="V116" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="3:22">
+    <row r="117" spans="2:22">
       <c r="C117" s="8" t="s">
         <v>544</v>
       </c>
@@ -9668,30 +9656,30 @@
       <c r="E117" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K117" s="47" t="s">
+      <c r="K117" s="39" t="s">
         <v>545</v>
       </c>
-      <c r="L117" s="43" t="s">
+      <c r="L117" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M117" s="26" t="s">
+      <c r="M117" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P117" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T117" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U117" s="59" t="s">
+      <c r="T117" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U117" s="53" t="s">
         <v>546</v>
       </c>
-      <c r="V117" s="60" t="s">
+      <c r="V117" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="3:22">
+    <row r="118" spans="2:22">
       <c r="C118" s="8" t="s">
         <v>547</v>
       </c>
@@ -9701,172 +9689,172 @@
       <c r="E118" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K118" s="47" t="s">
+      <c r="K118" s="39" t="s">
         <v>548</v>
       </c>
-      <c r="L118" s="43" t="s">
+      <c r="L118" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M118" s="26" t="s">
+      <c r="M118" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P118" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T118" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U118" s="59" t="s">
+      <c r="T118" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U118" s="53" t="s">
         <v>549</v>
       </c>
-      <c r="V118" s="60" t="s">
+      <c r="V118" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="3:22">
-      <c r="C119" s="73" t="s">
+    <row r="119" spans="2:22">
+      <c r="C119" s="75" t="s">
         <v>550</v>
       </c>
-      <c r="D119" s="74" t="s">
+      <c r="D119" s="76" t="s">
         <v>550</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K119" s="47" t="s">
+      <c r="K119" s="39" t="s">
         <v>551</v>
       </c>
-      <c r="L119" s="43" t="s">
+      <c r="L119" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M119" s="26" t="s">
+      <c r="M119" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P119" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T119" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U119" s="59" t="s">
+      <c r="T119" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U119" s="53" t="s">
         <v>552</v>
       </c>
-      <c r="V119" s="60" t="s">
+      <c r="V119" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="3:22">
-      <c r="C120" s="75" t="s">
+    <row r="120" spans="2:22">
+      <c r="C120" s="77" t="s">
         <v>553</v>
       </c>
-      <c r="D120" s="76" t="s">
+      <c r="D120" s="78" t="s">
         <v>458</v>
       </c>
-      <c r="E120" s="36" t="s">
+      <c r="E120" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K120" s="47" t="s">
+      <c r="K120" s="39" t="s">
         <v>554</v>
       </c>
-      <c r="L120" s="43" t="s">
+      <c r="L120" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M120" s="26" t="s">
+      <c r="M120" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P120" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T120" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U120" s="59" t="s">
+      <c r="T120" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U120" s="53" t="s">
         <v>555</v>
       </c>
-      <c r="V120" s="60" t="s">
+      <c r="V120" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="121" spans="2:22">
-      <c r="B121" s="77" t="s">
+      <c r="B121" s="79" t="s">
         <v>556</v>
       </c>
-      <c r="C121" s="29" t="s">
+      <c r="C121" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="D121" s="30" t="s">
+      <c r="D121" s="50" t="s">
         <v>209</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K121" s="47" t="s">
+      <c r="K121" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="L121" s="43" t="s">
+      <c r="L121" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M121" s="26" t="s">
+      <c r="M121" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P121" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T121" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U121" s="59" t="s">
+      <c r="T121" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U121" s="53" t="s">
         <v>558</v>
       </c>
-      <c r="V121" s="60" t="s">
+      <c r="V121" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="122" spans="2:22">
-      <c r="B122" s="78" t="s">
+      <c r="B122" s="80" t="s">
         <v>559</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C122" s="49" t="s">
         <v>560</v>
       </c>
-      <c r="D122" s="30" t="s">
+      <c r="D122" s="50" t="s">
         <v>34</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K122" s="47" t="s">
+      <c r="K122" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="L122" s="43" t="s">
+      <c r="L122" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M122" s="26" t="s">
+      <c r="M122" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P122" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T122" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U122" s="59" t="s">
+      <c r="T122" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U122" s="53" t="s">
         <v>562</v>
       </c>
-      <c r="V122" s="60" t="s">
+      <c r="V122" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="123" spans="2:22">
-      <c r="B123" s="79" t="s">
+      <c r="B123" s="81" t="s">
         <v>563</v>
       </c>
-      <c r="C123" s="79" t="s">
+      <c r="C123" s="81" t="s">
         <v>563</v>
       </c>
       <c r="D123" s="7" t="s">
@@ -9875,34 +9863,34 @@
       <c r="E123" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="K123" s="47" t="s">
+      <c r="K123" s="39" t="s">
         <v>564</v>
       </c>
-      <c r="L123" s="43" t="s">
+      <c r="L123" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M123" s="26" t="s">
+      <c r="M123" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P123" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T123" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U123" s="59" t="s">
+      <c r="T123" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U123" s="53" t="s">
         <v>565</v>
       </c>
-      <c r="V123" s="60" t="s">
+      <c r="V123" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="124" spans="2:22">
-      <c r="B124" s="80" t="s">
+      <c r="B124" s="82" t="s">
         <v>566</v>
       </c>
-      <c r="C124" s="80" t="s">
+      <c r="C124" s="82" t="s">
         <v>566</v>
       </c>
       <c r="D124" s="4" t="s">
@@ -9911,664 +9899,664 @@
       <c r="E124" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K124" s="47" t="s">
+      <c r="K124" s="39" t="s">
         <v>567</v>
       </c>
-      <c r="L124" s="43" t="s">
+      <c r="L124" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M124" s="26" t="s">
+      <c r="M124" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P124" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T124" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U124" s="59" t="s">
+      <c r="T124" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U124" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="V124" s="60" t="s">
+      <c r="V124" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="3:22">
+    <row r="125" spans="2:22">
       <c r="C125" s="1"/>
       <c r="D125" s="5"/>
-      <c r="K125" s="47" t="s">
+      <c r="K125" s="39" t="s">
         <v>569</v>
       </c>
-      <c r="L125" s="43" t="s">
+      <c r="L125" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M125" s="26" t="s">
+      <c r="M125" s="40" t="s">
         <v>216</v>
       </c>
       <c r="P125" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T125" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U125" s="59" t="s">
+      <c r="T125" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U125" s="53" t="s">
         <v>570</v>
       </c>
-      <c r="V125" s="60" t="s">
+      <c r="V125" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="3:22">
+    <row r="126" spans="2:22">
       <c r="C126" s="1"/>
       <c r="D126" s="5"/>
-      <c r="K126" s="47" t="s">
+      <c r="K126" s="39" t="s">
         <v>571</v>
       </c>
-      <c r="L126" s="43" t="s">
+      <c r="L126" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M126" s="50" t="s">
+      <c r="M126" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P126" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T126" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U126" s="59" t="s">
+      <c r="T126" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U126" s="53" t="s">
         <v>572</v>
       </c>
-      <c r="V126" s="60" t="s">
+      <c r="V126" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="3:22">
+    <row r="127" spans="2:22">
       <c r="C127" s="1"/>
       <c r="D127" s="5"/>
-      <c r="K127" s="47" t="s">
+      <c r="K127" s="39" t="s">
         <v>573</v>
       </c>
-      <c r="L127" s="43" t="s">
+      <c r="L127" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M127" s="50" t="s">
+      <c r="M127" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P127" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T127" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U127" s="59" t="s">
+      <c r="T127" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U127" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="V127" s="60" t="s">
+      <c r="V127" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="11:22">
-      <c r="K128" s="47" t="s">
+    <row r="128" spans="2:22">
+      <c r="K128" s="39" t="s">
         <v>575</v>
       </c>
-      <c r="L128" s="43" t="s">
+      <c r="L128" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="M128" s="50" t="s">
+      <c r="M128" s="52" t="s">
         <v>260</v>
       </c>
       <c r="P128" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T128" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U128" s="59" t="s">
+      <c r="T128" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U128" s="53" t="s">
         <v>576</v>
       </c>
-      <c r="V128" s="60" t="s">
+      <c r="V128" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="11:22">
-      <c r="K129" s="47" t="s">
+    <row r="129" spans="3:22">
+      <c r="K129" s="39" t="s">
         <v>577</v>
       </c>
-      <c r="L129" s="43" t="s">
+      <c r="L129" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M129" s="50">
+      <c r="M129" s="52">
         <v>48</v>
       </c>
       <c r="P129" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T129" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U129" s="59" t="s">
+      <c r="T129" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U129" s="53" t="s">
         <v>578</v>
       </c>
-      <c r="V129" s="60" t="s">
+      <c r="V129" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="130" spans="3:22">
       <c r="C130" s="1"/>
       <c r="D130" s="5"/>
-      <c r="K130" s="47" t="s">
+      <c r="K130" s="39" t="s">
         <v>579</v>
       </c>
-      <c r="L130" s="43" t="s">
+      <c r="L130" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M130" s="50">
+      <c r="M130" s="52">
         <v>48</v>
       </c>
       <c r="P130" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T130" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U130" s="59" t="s">
+      <c r="T130" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U130" s="53" t="s">
         <v>580</v>
       </c>
-      <c r="V130" s="60" t="s">
+      <c r="V130" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="131" spans="3:22">
       <c r="C131" s="1"/>
       <c r="D131" s="5"/>
-      <c r="K131" s="47" t="s">
+      <c r="K131" s="39" t="s">
         <v>581</v>
       </c>
-      <c r="L131" s="43" t="s">
+      <c r="L131" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M131" s="50">
+      <c r="M131" s="52">
         <v>48</v>
       </c>
       <c r="P131" s="8" t="str">
         <f t="shared" ref="P131:P166" si="2">N131&amp;O131</f>
         <v/>
       </c>
-      <c r="T131" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U131" s="59" t="s">
+      <c r="T131" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U131" s="53" t="s">
         <v>582</v>
       </c>
-      <c r="V131" s="60" t="s">
+      <c r="V131" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="132" spans="3:22">
       <c r="C132" s="1"/>
       <c r="D132" s="5"/>
-      <c r="K132" s="47" t="s">
+      <c r="K132" s="39" t="s">
         <v>583</v>
       </c>
-      <c r="L132" s="43" t="s">
+      <c r="L132" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M132" s="50">
+      <c r="M132" s="52">
         <v>48</v>
       </c>
       <c r="P132" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T132" s="55" t="s">
+      <c r="T132" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U132" s="83" t="s">
         <v>584</v>
       </c>
-      <c r="V132" s="60" t="s">
+      <c r="V132" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="133" spans="3:22">
       <c r="C133" s="1"/>
       <c r="D133" s="5"/>
-      <c r="K133" s="47" t="s">
+      <c r="K133" s="39" t="s">
         <v>585</v>
       </c>
-      <c r="L133" s="43" t="s">
+      <c r="L133" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M133" s="50">
+      <c r="M133" s="52">
         <v>48</v>
       </c>
       <c r="P133" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T133" s="55" t="s">
+      <c r="T133" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U133" s="83" t="s">
         <v>586</v>
       </c>
-      <c r="V133" s="60" t="s">
+      <c r="V133" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="134" spans="3:22">
       <c r="C134" s="1"/>
       <c r="D134" s="5"/>
-      <c r="K134" s="47" t="s">
+      <c r="K134" s="39" t="s">
         <v>587</v>
       </c>
-      <c r="L134" s="43" t="s">
+      <c r="L134" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M134" s="50">
+      <c r="M134" s="52">
         <v>48</v>
       </c>
       <c r="P134" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T134" s="55" t="s">
+      <c r="T134" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U134" s="83" t="s">
         <v>588</v>
       </c>
-      <c r="V134" s="60" t="s">
+      <c r="V134" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="135" spans="3:22">
       <c r="C135" s="1"/>
       <c r="D135" s="5"/>
-      <c r="K135" s="47" t="s">
+      <c r="K135" s="39" t="s">
         <v>589</v>
       </c>
-      <c r="L135" s="43" t="s">
+      <c r="L135" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M135" s="50">
+      <c r="M135" s="52">
         <v>48</v>
       </c>
       <c r="P135" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T135" s="55" t="s">
+      <c r="T135" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U135" s="83" t="s">
         <v>590</v>
       </c>
-      <c r="V135" s="60" t="s">
+      <c r="V135" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="136" spans="3:22">
       <c r="C136" s="1"/>
       <c r="D136" s="5"/>
-      <c r="K136" s="47" t="s">
+      <c r="K136" s="39" t="s">
         <v>591</v>
       </c>
-      <c r="L136" s="43" t="s">
+      <c r="L136" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M136" s="26" t="s">
+      <c r="M136" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P136" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T136" s="55" t="s">
+      <c r="T136" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U136" s="83" t="s">
         <v>592</v>
       </c>
-      <c r="V136" s="60" t="s">
+      <c r="V136" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="137" spans="3:22">
       <c r="C137" s="1"/>
       <c r="D137" s="5"/>
-      <c r="K137" s="47" t="s">
+      <c r="K137" s="39" t="s">
         <v>593</v>
       </c>
-      <c r="L137" s="43" t="s">
+      <c r="L137" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M137" s="26" t="s">
+      <c r="M137" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P137" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T137" s="55" t="s">
+      <c r="T137" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U137" s="83" t="s">
         <v>594</v>
       </c>
-      <c r="V137" s="60" t="s">
+      <c r="V137" s="54" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="11:22">
-      <c r="K138" s="47" t="s">
+    <row r="138" spans="3:22">
+      <c r="K138" s="39" t="s">
         <v>595</v>
       </c>
-      <c r="L138" s="43" t="s">
+      <c r="L138" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M138" s="26" t="s">
+      <c r="M138" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P138" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T138" s="55" t="s">
+      <c r="T138" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U138" s="83" t="s">
         <v>596</v>
       </c>
-      <c r="V138" s="60" t="s">
+      <c r="V138" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="139" spans="3:22">
       <c r="C139" s="1"/>
       <c r="D139" s="5"/>
-      <c r="K139" s="47" t="s">
+      <c r="K139" s="39" t="s">
         <v>597</v>
       </c>
-      <c r="L139" s="43" t="s">
+      <c r="L139" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M139" s="26" t="s">
+      <c r="M139" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P139" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T139" s="55" t="s">
+      <c r="T139" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U139" s="83" t="s">
         <v>598</v>
       </c>
-      <c r="V139" s="60" t="s">
+      <c r="V139" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="140" spans="3:22">
       <c r="C140" s="1"/>
       <c r="D140" s="5"/>
-      <c r="K140" s="47" t="s">
+      <c r="K140" s="39" t="s">
         <v>599</v>
       </c>
-      <c r="L140" s="43" t="s">
+      <c r="L140" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M140" s="26" t="s">
+      <c r="M140" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P140" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T140" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U140" s="59" t="s">
+      <c r="T140" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U140" s="53" t="s">
         <v>600</v>
       </c>
-      <c r="V140" s="60" t="s">
+      <c r="V140" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="141" spans="3:22">
       <c r="C141" s="1"/>
       <c r="D141" s="5"/>
-      <c r="K141" s="47" t="s">
+      <c r="K141" s="39" t="s">
         <v>601</v>
       </c>
-      <c r="L141" s="43" t="s">
+      <c r="L141" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M141" s="26" t="s">
+      <c r="M141" s="40" t="s">
         <v>507</v>
       </c>
       <c r="P141" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T141" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U141" s="59" t="s">
+      <c r="T141" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U141" s="53" t="s">
         <v>602</v>
       </c>
-      <c r="V141" s="60" t="s">
+      <c r="V141" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="142" spans="3:22">
       <c r="C142" s="1"/>
       <c r="D142" s="5"/>
-      <c r="K142" s="47" t="s">
+      <c r="K142" s="39" t="s">
         <v>603</v>
       </c>
-      <c r="L142" s="43" t="s">
+      <c r="L142" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M142" s="26">
+      <c r="M142" s="40">
         <v>48</v>
       </c>
       <c r="P142" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T142" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U142" s="59" t="s">
+      <c r="T142" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U142" s="53" t="s">
         <v>604</v>
       </c>
-      <c r="V142" s="60" t="s">
+      <c r="V142" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="143" spans="3:22">
       <c r="C143" s="1"/>
       <c r="D143" s="5"/>
-      <c r="K143" s="47" t="s">
+      <c r="K143" s="39" t="s">
         <v>605</v>
       </c>
-      <c r="L143" s="43" t="s">
+      <c r="L143" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M143" s="26">
+      <c r="M143" s="40">
         <v>48</v>
       </c>
       <c r="P143" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T143" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="U143" s="59" t="s">
+      <c r="T143" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="U143" s="53" t="s">
         <v>606</v>
       </c>
-      <c r="V143" s="60" t="s">
+      <c r="V143" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="144" spans="3:22">
       <c r="C144" s="1"/>
       <c r="D144" s="5"/>
-      <c r="K144" s="47" t="s">
+      <c r="K144" s="39" t="s">
         <v>607</v>
       </c>
-      <c r="L144" s="43" t="s">
+      <c r="L144" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M144" s="26">
+      <c r="M144" s="40">
         <v>48</v>
       </c>
       <c r="P144" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T144" s="55" t="s">
+      <c r="T144" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U144" s="84" t="s">
         <v>608</v>
       </c>
-      <c r="V144" s="60" t="s">
+      <c r="V144" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="145" spans="3:22">
       <c r="C145" s="1"/>
       <c r="D145" s="5"/>
-      <c r="K145" s="47" t="s">
+      <c r="K145" s="39" t="s">
         <v>609</v>
       </c>
-      <c r="L145" s="43" t="s">
+      <c r="L145" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M145" s="26">
+      <c r="M145" s="40">
         <v>48</v>
       </c>
       <c r="P145" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T145" s="55" t="s">
+      <c r="T145" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U145" s="84" t="s">
         <v>610</v>
       </c>
-      <c r="V145" s="60" t="s">
+      <c r="V145" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="146" spans="3:22">
       <c r="C146" s="1"/>
       <c r="D146" s="5"/>
-      <c r="K146" s="47" t="s">
+      <c r="K146" s="39" t="s">
         <v>611</v>
       </c>
-      <c r="L146" s="43" t="s">
+      <c r="L146" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M146" s="26">
+      <c r="M146" s="40">
         <v>48</v>
       </c>
       <c r="P146" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T146" s="55" t="s">
+      <c r="T146" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U146" s="84" t="s">
         <v>612</v>
       </c>
-      <c r="V146" s="60" t="s">
+      <c r="V146" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="147" spans="3:22">
       <c r="C147" s="1"/>
       <c r="D147" s="5"/>
-      <c r="K147" s="47" t="s">
+      <c r="K147" s="39" t="s">
         <v>613</v>
       </c>
-      <c r="L147" s="43" t="s">
+      <c r="L147" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M147" s="26">
+      <c r="M147" s="40">
         <v>48</v>
       </c>
       <c r="P147" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T147" s="55" t="s">
+      <c r="T147" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U147" s="85" t="s">
         <v>614</v>
       </c>
-      <c r="V147" s="60" t="s">
+      <c r="V147" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="148" spans="3:22">
       <c r="C148" s="1"/>
       <c r="D148" s="5"/>
-      <c r="K148" s="47" t="s">
+      <c r="K148" s="39" t="s">
         <v>615</v>
       </c>
-      <c r="L148" s="43" t="s">
+      <c r="L148" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M148" s="26">
+      <c r="M148" s="40">
         <v>48</v>
       </c>
       <c r="P148" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T148" s="55" t="s">
+      <c r="T148" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U148" s="85" t="s">
         <v>616</v>
       </c>
-      <c r="V148" s="60" t="s">
+      <c r="V148" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="149" spans="3:22">
       <c r="C149" s="1"/>
       <c r="D149" s="5"/>
-      <c r="K149" s="47" t="s">
+      <c r="K149" s="39" t="s">
         <v>617</v>
       </c>
-      <c r="L149" s="43" t="s">
+      <c r="L149" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M149" s="26">
+      <c r="M149" s="40">
         <v>48</v>
       </c>
       <c r="P149" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T149" s="55" t="s">
+      <c r="T149" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U149" s="7" t="s">
@@ -10578,21 +10566,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" spans="11:22">
-      <c r="K150" s="47" t="s">
+    <row r="150" spans="3:22">
+      <c r="K150" s="39" t="s">
         <v>619</v>
       </c>
-      <c r="L150" s="43" t="s">
+      <c r="L150" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M150" s="26">
+      <c r="M150" s="40">
         <v>48</v>
       </c>
       <c r="P150" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T150" s="55" t="s">
+      <c r="T150" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U150" s="7" t="s">
@@ -10602,21 +10590,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="11:22">
-      <c r="K151" s="47" t="s">
+    <row r="151" spans="3:22">
+      <c r="K151" s="39" t="s">
         <v>621</v>
       </c>
-      <c r="L151" s="43" t="s">
+      <c r="L151" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M151" s="26">
+      <c r="M151" s="40">
         <v>48</v>
       </c>
       <c r="P151" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T151" s="55" t="s">
+      <c r="T151" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U151" s="7" t="s">
@@ -10626,21 +10614,21 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="11:22">
-      <c r="K152" s="47" t="s">
+    <row r="152" spans="3:22">
+      <c r="K152" s="39" t="s">
         <v>623</v>
       </c>
-      <c r="L152" s="43" t="s">
+      <c r="L152" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M152" s="26">
+      <c r="M152" s="40">
         <v>48</v>
       </c>
       <c r="P152" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T152" s="55" t="s">
+      <c r="T152" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U152" s="7" t="s">
@@ -10650,21 +10638,21 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="11:22">
-      <c r="K153" s="47" t="s">
+    <row r="153" spans="3:22">
+      <c r="K153" s="39" t="s">
         <v>625</v>
       </c>
-      <c r="L153" s="43" t="s">
+      <c r="L153" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M153" s="26">
+      <c r="M153" s="40">
         <v>48</v>
       </c>
       <c r="P153" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T153" s="55"/>
+      <c r="T153" s="41"/>
       <c r="U153" s="86" t="s">
         <v>626</v>
       </c>
@@ -10675,20 +10663,20 @@
     <row r="154" spans="3:22">
       <c r="C154" s="1"/>
       <c r="D154" s="5"/>
-      <c r="K154" s="47" t="s">
+      <c r="K154" s="39" t="s">
         <v>627</v>
       </c>
-      <c r="L154" s="43" t="s">
+      <c r="L154" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="M154" s="26">
+      <c r="M154" s="40">
         <v>48</v>
       </c>
       <c r="P154" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T154" s="55"/>
+      <c r="T154" s="41"/>
       <c r="U154" s="86" t="s">
         <v>628</v>
       </c>
@@ -10699,20 +10687,20 @@
     <row r="155" spans="3:22">
       <c r="C155" s="1"/>
       <c r="D155" s="5"/>
-      <c r="K155" s="47" t="s">
+      <c r="K155" s="39" t="s">
         <v>629</v>
       </c>
-      <c r="L155" s="43" t="s">
+      <c r="L155" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M155" s="26">
+      <c r="M155" s="40">
         <v>48</v>
       </c>
       <c r="P155" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T155" s="55"/>
+      <c r="T155" s="41"/>
       <c r="U155" s="86" t="s">
         <v>630</v>
       </c>
@@ -10723,20 +10711,20 @@
     <row r="156" spans="3:22">
       <c r="C156" s="1"/>
       <c r="D156" s="5"/>
-      <c r="K156" s="47" t="s">
+      <c r="K156" s="39" t="s">
         <v>631</v>
       </c>
-      <c r="L156" s="43" t="s">
+      <c r="L156" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M156" s="26">
+      <c r="M156" s="40">
         <v>48</v>
       </c>
       <c r="P156" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T156" s="55"/>
+      <c r="T156" s="41"/>
       <c r="U156" s="86" t="s">
         <v>632</v>
       </c>
@@ -10747,20 +10735,20 @@
     <row r="157" spans="3:22">
       <c r="C157" s="1"/>
       <c r="D157" s="5"/>
-      <c r="K157" s="47" t="s">
+      <c r="K157" s="39" t="s">
         <v>633</v>
       </c>
-      <c r="L157" s="43" t="s">
+      <c r="L157" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M157" s="26">
+      <c r="M157" s="40">
         <v>48</v>
       </c>
       <c r="P157" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T157" s="55"/>
+      <c r="T157" s="41"/>
       <c r="U157" s="86" t="s">
         <v>634</v>
       </c>
@@ -10768,23 +10756,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" ht="31.2" spans="3:22">
+    <row r="158" ht="28.5" spans="3:22">
       <c r="C158" s="1"/>
       <c r="D158" s="5"/>
-      <c r="K158" s="47" t="s">
+      <c r="K158" s="39" t="s">
         <v>635</v>
       </c>
-      <c r="L158" s="43" t="s">
+      <c r="L158" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M158" s="26">
+      <c r="M158" s="40">
         <v>48</v>
       </c>
       <c r="P158" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T158" s="55"/>
+      <c r="T158" s="41"/>
       <c r="U158" s="86" t="s">
         <v>636</v>
       </c>
@@ -10795,20 +10783,20 @@
     <row r="159" spans="3:22">
       <c r="C159" s="1"/>
       <c r="D159" s="5"/>
-      <c r="K159" s="47" t="s">
+      <c r="K159" s="39" t="s">
         <v>638</v>
       </c>
-      <c r="L159" s="43" t="s">
+      <c r="L159" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M159" s="26" t="s">
+      <c r="M159" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P159" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T159" s="55"/>
+      <c r="T159" s="41"/>
       <c r="U159" s="86" t="s">
         <v>639</v>
       </c>
@@ -10819,20 +10807,20 @@
     <row r="160" spans="3:22">
       <c r="C160" s="1"/>
       <c r="D160" s="5"/>
-      <c r="K160" s="47" t="s">
+      <c r="K160" s="39" t="s">
         <v>640</v>
       </c>
-      <c r="L160" s="43" t="s">
+      <c r="L160" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M160" s="26" t="s">
+      <c r="M160" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P160" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T160" s="55"/>
+      <c r="T160" s="41"/>
       <c r="U160" s="89" t="s">
         <v>641</v>
       </c>
@@ -10843,20 +10831,20 @@
     <row r="161" spans="3:22">
       <c r="C161" s="1"/>
       <c r="D161" s="5"/>
-      <c r="K161" s="47" t="s">
+      <c r="K161" s="39" t="s">
         <v>642</v>
       </c>
-      <c r="L161" s="43" t="s">
+      <c r="L161" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M161" s="26" t="s">
+      <c r="M161" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P161" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T161" s="55"/>
+      <c r="T161" s="41"/>
       <c r="U161" s="86"/>
       <c r="V161" s="90"/>
     </row>
@@ -10865,100 +10853,100 @@
         <v>553</v>
       </c>
       <c r="D162" s="5"/>
-      <c r="K162" s="47" t="s">
+      <c r="K162" s="39" t="s">
         <v>643</v>
       </c>
-      <c r="L162" s="43" t="s">
+      <c r="L162" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M162" s="26" t="s">
+      <c r="M162" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P162" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T162" s="55"/>
+      <c r="T162" s="41"/>
       <c r="U162" s="86"/>
       <c r="V162" s="90"/>
     </row>
     <row r="163" spans="3:22">
       <c r="C163" s="1"/>
       <c r="D163" s="5"/>
-      <c r="K163" s="47" t="s">
+      <c r="K163" s="39" t="s">
         <v>644</v>
       </c>
-      <c r="L163" s="43" t="s">
+      <c r="L163" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M163" s="26" t="s">
+      <c r="M163" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P163" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T163" s="55"/>
+      <c r="T163" s="41"/>
       <c r="U163" s="86"/>
       <c r="V163" s="87"/>
     </row>
     <row r="164" spans="3:22">
       <c r="C164" s="1"/>
       <c r="D164" s="5"/>
-      <c r="K164" s="47" t="s">
+      <c r="K164" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="L164" s="43" t="s">
+      <c r="L164" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M164" s="26" t="s">
+      <c r="M164" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P164" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T164" s="55"/>
+      <c r="T164" s="41"/>
       <c r="U164" s="86"/>
       <c r="V164" s="90"/>
     </row>
     <row r="165" spans="3:22">
       <c r="C165" s="1"/>
       <c r="D165" s="5"/>
-      <c r="K165" s="47" t="s">
+      <c r="K165" s="39" t="s">
         <v>646</v>
       </c>
-      <c r="L165" s="43" t="s">
+      <c r="L165" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M165" s="26" t="s">
+      <c r="M165" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P165" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T165" s="55"/>
+      <c r="T165" s="41"/>
       <c r="U165" s="86"/>
       <c r="V165" s="90"/>
     </row>
     <row r="166" spans="3:22">
       <c r="C166" s="1"/>
       <c r="D166" s="5"/>
-      <c r="K166" s="47" t="s">
+      <c r="K166" s="39" t="s">
         <v>647</v>
       </c>
-      <c r="L166" s="43" t="s">
+      <c r="L166" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="M166" s="26" t="s">
+      <c r="M166" s="40" t="s">
         <v>266</v>
       </c>
       <c r="P166" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="T166" s="55"/>
+      <c r="T166" s="41"/>
       <c r="U166" s="86"/>
       <c r="V166" s="87"/>
     </row>

--- a/data/0.rule.xlsx
+++ b/data/0.rule.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="651">
   <si>
     <t>病象 责任部门 对照表</t>
   </si>
@@ -1869,6 +1869,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>胎体帘线接头开</t>
     </r>
     <r>
@@ -2867,6 +2872,26 @@
   </si>
   <si>
     <t>T06774</t>
+  </si>
+  <si>
+    <r>
+      <t>修伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ซ่อมเสียหาย</t>
+    </r>
+  </si>
+  <si>
+    <t>修伤</t>
+  </si>
+  <si>
+    <t>T.I</t>
   </si>
   <si>
     <t>TC-LH-S09</t>
@@ -3366,15 +3391,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="36">
@@ -9923,10 +9948,20 @@
       </c>
     </row>
     <row r="125" spans="2:22">
-      <c r="C125" s="1"/>
-      <c r="D125" s="5"/>
+      <c r="B125" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="K125" s="39" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L125" s="28" t="s">
         <v>72</v>
@@ -9942,7 +9977,7 @@
         <v>29</v>
       </c>
       <c r="U125" s="53" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="V125" s="54" t="s">
         <v>26</v>
@@ -9952,7 +9987,7 @@
       <c r="C126" s="1"/>
       <c r="D126" s="5"/>
       <c r="K126" s="39" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L126" s="28" t="s">
         <v>72</v>
@@ -9968,7 +10003,7 @@
         <v>29</v>
       </c>
       <c r="U126" s="53" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="V126" s="54" t="s">
         <v>26</v>
@@ -9978,7 +10013,7 @@
       <c r="C127" s="1"/>
       <c r="D127" s="5"/>
       <c r="K127" s="39" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L127" s="28" t="s">
         <v>72</v>
@@ -9994,7 +10029,7 @@
         <v>29</v>
       </c>
       <c r="U127" s="53" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="V127" s="54" t="s">
         <v>26</v>
@@ -10002,7 +10037,7 @@
     </row>
     <row r="128" spans="2:22">
       <c r="K128" s="39" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="L128" s="28" t="s">
         <v>72</v>
@@ -10018,7 +10053,7 @@
         <v>29</v>
       </c>
       <c r="U128" s="53" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="V128" s="54" t="s">
         <v>26</v>
@@ -10026,7 +10061,7 @@
     </row>
     <row r="129" spans="3:22">
       <c r="K129" s="39" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L129" s="28" t="s">
         <v>55</v>
@@ -10042,7 +10077,7 @@
         <v>29</v>
       </c>
       <c r="U129" s="53" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="V129" s="54" t="s">
         <v>26</v>
@@ -10052,7 +10087,7 @@
       <c r="C130" s="1"/>
       <c r="D130" s="5"/>
       <c r="K130" s="39" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="L130" s="28" t="s">
         <v>55</v>
@@ -10068,7 +10103,7 @@
         <v>29</v>
       </c>
       <c r="U130" s="53" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="V130" s="54" t="s">
         <v>26</v>
@@ -10078,7 +10113,7 @@
       <c r="C131" s="1"/>
       <c r="D131" s="5"/>
       <c r="K131" s="39" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L131" s="28" t="s">
         <v>55</v>
@@ -10094,7 +10129,7 @@
         <v>29</v>
       </c>
       <c r="U131" s="53" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="V131" s="54" t="s">
         <v>26</v>
@@ -10104,7 +10139,7 @@
       <c r="C132" s="1"/>
       <c r="D132" s="5"/>
       <c r="K132" s="39" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L132" s="28" t="s">
         <v>55</v>
@@ -10120,7 +10155,7 @@
         <v>29</v>
       </c>
       <c r="U132" s="83" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="V132" s="54" t="s">
         <v>26</v>
@@ -10130,7 +10165,7 @@
       <c r="C133" s="1"/>
       <c r="D133" s="5"/>
       <c r="K133" s="39" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L133" s="28" t="s">
         <v>55</v>
@@ -10146,7 +10181,7 @@
         <v>29</v>
       </c>
       <c r="U133" s="83" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="V133" s="54" t="s">
         <v>26</v>
@@ -10156,7 +10191,7 @@
       <c r="C134" s="1"/>
       <c r="D134" s="5"/>
       <c r="K134" s="39" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L134" s="28" t="s">
         <v>55</v>
@@ -10172,7 +10207,7 @@
         <v>29</v>
       </c>
       <c r="U134" s="83" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="V134" s="54" t="s">
         <v>26</v>
@@ -10182,7 +10217,7 @@
       <c r="C135" s="1"/>
       <c r="D135" s="5"/>
       <c r="K135" s="39" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L135" s="28" t="s">
         <v>55</v>
@@ -10198,7 +10233,7 @@
         <v>29</v>
       </c>
       <c r="U135" s="83" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="V135" s="54" t="s">
         <v>26</v>
@@ -10208,7 +10243,7 @@
       <c r="C136" s="1"/>
       <c r="D136" s="5"/>
       <c r="K136" s="39" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L136" s="28" t="s">
         <v>55</v>
@@ -10224,7 +10259,7 @@
         <v>29</v>
       </c>
       <c r="U136" s="83" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="V136" s="54" t="s">
         <v>26</v>
@@ -10234,7 +10269,7 @@
       <c r="C137" s="1"/>
       <c r="D137" s="5"/>
       <c r="K137" s="39" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L137" s="28" t="s">
         <v>55</v>
@@ -10250,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="U137" s="83" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="V137" s="54" t="s">
         <v>26</v>
@@ -10258,7 +10293,7 @@
     </row>
     <row r="138" spans="3:22">
       <c r="K138" s="39" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L138" s="28" t="s">
         <v>55</v>
@@ -10274,7 +10309,7 @@
         <v>29</v>
       </c>
       <c r="U138" s="83" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="V138" s="54" t="s">
         <v>26</v>
@@ -10284,7 +10319,7 @@
       <c r="C139" s="1"/>
       <c r="D139" s="5"/>
       <c r="K139" s="39" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="L139" s="28" t="s">
         <v>55</v>
@@ -10300,7 +10335,7 @@
         <v>29</v>
       </c>
       <c r="U139" s="83" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="V139" s="54" t="s">
         <v>26</v>
@@ -10310,7 +10345,7 @@
       <c r="C140" s="1"/>
       <c r="D140" s="5"/>
       <c r="K140" s="39" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="L140" s="28" t="s">
         <v>55</v>
@@ -10326,7 +10361,7 @@
         <v>29</v>
       </c>
       <c r="U140" s="53" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="V140" s="54" t="s">
         <v>26</v>
@@ -10336,7 +10371,7 @@
       <c r="C141" s="1"/>
       <c r="D141" s="5"/>
       <c r="K141" s="39" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L141" s="28" t="s">
         <v>55</v>
@@ -10352,7 +10387,7 @@
         <v>29</v>
       </c>
       <c r="U141" s="53" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="V141" s="54" t="s">
         <v>26</v>
@@ -10362,7 +10397,7 @@
       <c r="C142" s="1"/>
       <c r="D142" s="5"/>
       <c r="K142" s="39" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L142" s="28" t="s">
         <v>32</v>
@@ -10378,7 +10413,7 @@
         <v>29</v>
       </c>
       <c r="U142" s="53" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="V142" s="54" t="s">
         <v>26</v>
@@ -10388,7 +10423,7 @@
       <c r="C143" s="1"/>
       <c r="D143" s="5"/>
       <c r="K143" s="39" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="L143" s="28" t="s">
         <v>32</v>
@@ -10404,7 +10439,7 @@
         <v>29</v>
       </c>
       <c r="U143" s="53" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="V143" s="54" t="s">
         <v>26</v>
@@ -10414,7 +10449,7 @@
       <c r="C144" s="1"/>
       <c r="D144" s="5"/>
       <c r="K144" s="39" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L144" s="28" t="s">
         <v>32</v>
@@ -10430,7 +10465,7 @@
         <v>29</v>
       </c>
       <c r="U144" s="84" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="V144" s="54" t="s">
         <v>26</v>
@@ -10440,7 +10475,7 @@
       <c r="C145" s="1"/>
       <c r="D145" s="5"/>
       <c r="K145" s="39" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="L145" s="28" t="s">
         <v>32</v>
@@ -10456,7 +10491,7 @@
         <v>29</v>
       </c>
       <c r="U145" s="84" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="V145" s="54" t="s">
         <v>26</v>
@@ -10466,7 +10501,7 @@
       <c r="C146" s="1"/>
       <c r="D146" s="5"/>
       <c r="K146" s="39" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L146" s="28" t="s">
         <v>32</v>
@@ -10482,7 +10517,7 @@
         <v>29</v>
       </c>
       <c r="U146" s="84" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="V146" s="54" t="s">
         <v>26</v>
@@ -10492,7 +10527,7 @@
       <c r="C147" s="1"/>
       <c r="D147" s="5"/>
       <c r="K147" s="39" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="L147" s="28" t="s">
         <v>32</v>
@@ -10508,7 +10543,7 @@
         <v>29</v>
       </c>
       <c r="U147" s="85" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="V147" s="54" t="s">
         <v>26</v>
@@ -10518,7 +10553,7 @@
       <c r="C148" s="1"/>
       <c r="D148" s="5"/>
       <c r="K148" s="39" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="L148" s="28" t="s">
         <v>32</v>
@@ -10534,7 +10569,7 @@
         <v>29</v>
       </c>
       <c r="U148" s="85" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="V148" s="54" t="s">
         <v>26</v>
@@ -10544,7 +10579,7 @@
       <c r="C149" s="1"/>
       <c r="D149" s="5"/>
       <c r="K149" s="39" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L149" s="28" t="s">
         <v>32</v>
@@ -10560,7 +10595,7 @@
         <v>29</v>
       </c>
       <c r="U149" s="7" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="V149" s="7" t="s">
         <v>31</v>
@@ -10568,7 +10603,7 @@
     </row>
     <row r="150" spans="3:22">
       <c r="K150" s="39" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L150" s="28" t="s">
         <v>32</v>
@@ -10584,7 +10619,7 @@
         <v>29</v>
       </c>
       <c r="U150" s="7" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="V150" s="8" t="s">
         <v>56</v>
@@ -10592,7 +10627,7 @@
     </row>
     <row r="151" spans="3:22">
       <c r="K151" s="39" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="L151" s="28" t="s">
         <v>32</v>
@@ -10608,7 +10643,7 @@
         <v>29</v>
       </c>
       <c r="U151" s="7" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="V151" s="8" t="s">
         <v>26</v>
@@ -10616,7 +10651,7 @@
     </row>
     <row r="152" spans="3:22">
       <c r="K152" s="39" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L152" s="28" t="s">
         <v>32</v>
@@ -10632,7 +10667,7 @@
         <v>29</v>
       </c>
       <c r="U152" s="7" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="V152" s="8" t="s">
         <v>26</v>
@@ -10640,7 +10675,7 @@
     </row>
     <row r="153" spans="3:22">
       <c r="K153" s="39" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="L153" s="28" t="s">
         <v>32</v>
@@ -10654,7 +10689,7 @@
       </c>
       <c r="T153" s="41"/>
       <c r="U153" s="86" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="V153" s="87" t="s">
         <v>31</v>
@@ -10664,7 +10699,7 @@
       <c r="C154" s="1"/>
       <c r="D154" s="5"/>
       <c r="K154" s="39" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L154" s="28" t="s">
         <v>32</v>
@@ -10678,7 +10713,7 @@
       </c>
       <c r="T154" s="41"/>
       <c r="U154" s="86" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="V154" s="87" t="s">
         <v>31</v>
@@ -10688,7 +10723,7 @@
       <c r="C155" s="1"/>
       <c r="D155" s="5"/>
       <c r="K155" s="39" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L155" s="28" t="s">
         <v>130</v>
@@ -10702,7 +10737,7 @@
       </c>
       <c r="T155" s="41"/>
       <c r="U155" s="86" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="V155" s="87" t="s">
         <v>26</v>
@@ -10712,7 +10747,7 @@
       <c r="C156" s="1"/>
       <c r="D156" s="5"/>
       <c r="K156" s="39" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L156" s="28" t="s">
         <v>130</v>
@@ -10726,7 +10761,7 @@
       </c>
       <c r="T156" s="41"/>
       <c r="U156" s="86" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="V156" s="88" t="s">
         <v>31</v>
@@ -10736,7 +10771,7 @@
       <c r="C157" s="1"/>
       <c r="D157" s="5"/>
       <c r="K157" s="39" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L157" s="28" t="s">
         <v>130</v>
@@ -10750,7 +10785,7 @@
       </c>
       <c r="T157" s="41"/>
       <c r="U157" s="86" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="V157" s="88" t="s">
         <v>26</v>
@@ -10760,7 +10795,7 @@
       <c r="C158" s="1"/>
       <c r="D158" s="5"/>
       <c r="K158" s="39" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L158" s="28" t="s">
         <v>130</v>
@@ -10774,17 +10809,17 @@
       </c>
       <c r="T158" s="41"/>
       <c r="U158" s="86" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="V158" s="88" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="159" spans="3:22">
       <c r="C159" s="1"/>
       <c r="D159" s="5"/>
       <c r="K159" s="39" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L159" s="28" t="s">
         <v>130</v>
@@ -10798,7 +10833,7 @@
       </c>
       <c r="T159" s="41"/>
       <c r="U159" s="86" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="V159" s="87" t="s">
         <v>31</v>
@@ -10808,7 +10843,7 @@
       <c r="C160" s="1"/>
       <c r="D160" s="5"/>
       <c r="K160" s="39" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="L160" s="28" t="s">
         <v>130</v>
@@ -10822,7 +10857,7 @@
       </c>
       <c r="T160" s="41"/>
       <c r="U160" s="89" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="V160" s="87" t="s">
         <v>56</v>
@@ -10832,7 +10867,7 @@
       <c r="C161" s="1"/>
       <c r="D161" s="5"/>
       <c r="K161" s="39" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L161" s="28" t="s">
         <v>130</v>
@@ -10854,7 +10889,7 @@
       </c>
       <c r="D162" s="5"/>
       <c r="K162" s="39" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L162" s="28" t="s">
         <v>130</v>
@@ -10874,7 +10909,7 @@
       <c r="C163" s="1"/>
       <c r="D163" s="5"/>
       <c r="K163" s="39" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L163" s="28" t="s">
         <v>130</v>
@@ -10894,7 +10929,7 @@
       <c r="C164" s="1"/>
       <c r="D164" s="5"/>
       <c r="K164" s="39" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="L164" s="28" t="s">
         <v>130</v>
@@ -10914,7 +10949,7 @@
       <c r="C165" s="1"/>
       <c r="D165" s="5"/>
       <c r="K165" s="39" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="L165" s="28" t="s">
         <v>130</v>
@@ -10934,7 +10969,7 @@
       <c r="C166" s="1"/>
       <c r="D166" s="5"/>
       <c r="K166" s="39" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="L166" s="28" t="s">
         <v>130</v>

--- a/data/0.rule.xlsx
+++ b/data/0.rule.xlsx
@@ -1869,32 +1869,27 @@
   </si>
   <si>
     <r>
+      <t>胎体帘线接头开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>รอยต่อเส้นใยผ้าใบฉาบยางแยก</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>胎体帘线接头开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>รอยต่อเส้นใยผ้าใบฉาบยางแยก</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
-    <t>胎体接头开</t>
+    <t>胎体帘线接头开</t>
   </si>
   <si>
     <t>TC-LH-R02</t>
@@ -2875,6 +2870,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>修伤</t>
     </r>
     <r>

--- a/data/0.rule.xlsx
+++ b/data/0.rule.xlsx
@@ -1889,7 +1889,7 @@
     </r>
   </si>
   <si>
-    <t>胎体帘线接头开</t>
+    <t>胎体接头开</t>
   </si>
   <si>
     <t>TC-LH-R02</t>
@@ -3392,15 +3392,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="36">
